--- a/results/tables/hourly_prediction.xlsx
+++ b/results/tables/hourly_prediction.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>198.7842712402344</v>
+        <v>81.34810638427734</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>121.0263748168945</v>
+        <v>53.49015808105469</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>86.26566314697266</v>
+        <v>33.25905227661133</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45.55126190185547</v>
+        <v>32.015380859375</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58.72982788085938</v>
+        <v>29.84358978271484</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>214.8775177001953</v>
+        <v>130.4363708496094</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>487.3533935546875</v>
+        <v>246.6989288330078</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>930.0408935546875</v>
+        <v>252.0441589355469</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>765.5114135742188</v>
+        <v>162.4486083984375</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>684.5341796875</v>
+        <v>203.4707794189453</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>693.6552124023438</v>
+        <v>170.2646942138672</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1075.99267578125</v>
+        <v>243.4815979003906</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1300.016967773438</v>
+        <v>198.5749816894531</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>978.7977905273438</v>
+        <v>147.7231597900391</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>847.3021850585938</v>
+        <v>236.7548828125</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>789.2008056640625</v>
+        <v>84.80300140380859</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1237.407104492188</v>
+        <v>245.98291015625</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1951.3349609375</v>
+        <v>235.9208068847656</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1872.776489257812</v>
+        <v>99.98149871826172</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1607.84619140625</v>
+        <v>67.92855072021484</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1186.97900390625</v>
+        <v>23.0381965637207</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>734.5380859375</v>
+        <v>38.66020202636719</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>496.2821350097656</v>
+        <v>26.09228324890137</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>290.6377868652344</v>
+        <v>18.24177551269531</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>167.2708282470703</v>
+        <v>118.7700424194336</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>87.12413787841797</v>
+        <v>79.0667724609375</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>55.87985610961914</v>
+        <v>63.36428833007812</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>58.75662994384766</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5.562936305999756</v>
+        <v>44.55452346801758</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>132.9723358154297</v>
+        <v>142.8913879394531</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>309.3270568847656</v>
+        <v>265.2882995605469</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>502.3842163085938</v>
+        <v>250.6858367919922</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>618.48974609375</v>
+        <v>216.195068359375</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>703.50146484375</v>
+        <v>251.9441223144531</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>831.7986450195312</v>
+        <v>235.9330291748047</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>944.805908203125</v>
+        <v>258.4597778320312</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1095.0078125</v>
+        <v>288.5391845703125</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1151.523071289062</v>
+        <v>208.0726470947266</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1304.008544921875</v>
+        <v>283.5165710449219</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1035.748046875</v>
+        <v>112.6288681030273</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1075.726928710938</v>
+        <v>227.1239776611328</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>933.7063598632812</v>
+        <v>106.0858001708984</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>861.2313842773438</v>
+        <v>130.086669921875</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>766.7468872070312</v>
+        <v>96.07222747802734</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>621.2781372070312</v>
+        <v>53.14333343505859</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>511.675537109375</v>
+        <v>68.76545715332031</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>367.2706909179688</v>
+        <v>56.19747543334961</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>237.9979858398438</v>
+        <v>49.77550506591797</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>156.6165924072266</v>
+        <v>68.90352630615234</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>98.25143432617188</v>
+        <v>41.94034194946289</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>68.68711853027344</v>
+        <v>21.58189964294434</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>35.14831924438477</v>
+        <v>20.33823013305664</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>69.05941009521484</v>
+        <v>20.95535850524902</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>200.9936218261719</v>
+        <v>119.0669326782227</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>422.3494873046875</v>
+        <v>212.9118347167969</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>861.4869384765625</v>
+        <v>240.3670043945312</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>692.7396240234375</v>
+        <v>165.1163940429688</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>613.7787475585938</v>
+        <v>200.5235290527344</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>621.4732055664062</v>
+        <v>176.0921936035156</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1015.56494140625</v>
+        <v>233.9677276611328</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1213.968872070312</v>
+        <v>187.7848663330078</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>931.383056640625</v>
+        <v>137.34619140625</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>824.1035766601562</v>
+        <v>222.6149291992188</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>783.608642578125</v>
+        <v>73.12583160400391</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1169.495849609375</v>
+        <v>232.0908660888672</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2008.546997070312</v>
+        <v>260.0937194824219</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1796.567626953125</v>
+        <v>86.22464752197266</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1550.304565429688</v>
+        <v>56.25133514404297</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1080.6787109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>654.1231079101562</v>
+        <v>23.52226638793945</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>468.362060546875</v>
+        <v>17.63997459411621</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>231.7678833007812</v>
+        <v>8.690741539001465</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>120.9557113647461</v>
+        <v>104.4861068725586</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>49.3243408203125</v>
+        <v>65.67755126953125</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>29.90860939025879</v>
+        <v>49.84771347045898</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>44.24488067626953</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.74331951141357</v>
+        <v>33.82689666748047</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>102.4573287963867</v>
+        <v>129.6825866699219</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>256.7261047363281</v>
+        <v>230.5915985107422</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>445.4877319335938</v>
+        <v>237.1692657470703</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>555.8068237304688</v>
+        <v>218.9814910888672</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>644.9085083007812</v>
+        <v>247.1575164794922</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>743.71240234375</v>
+        <v>243.0895843505859</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>897.9366455078125</v>
+        <v>245.4072113037109</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1031.572387695312</v>
+        <v>275.9095458984375</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1109.84765625</v>
+        <v>195.8562622070312</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1267.379760742188</v>
+        <v>267.5370788574219</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1003.692199707031</v>
+        <v>99.11233520507812</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1008.218811035156</v>
+        <v>211.3925628662109</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>939.5073852539062</v>
+        <v>115.5783996582031</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>799.674072265625</v>
+        <v>114.4904708862305</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>710.30908203125</v>
+        <v>82.55567169189453</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>548.5610961914062</v>
+        <v>21.7487621307373</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>438.1067810058594</v>
+        <v>51.78805923461914</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>317.78271484375</v>
+        <v>45.90579223632812</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>182.6516418457031</v>
+        <v>38.38510513305664</v>
       </c>
     </row>
     <row r="98">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>87.98445892333984</v>
+        <v>55.67623519897461</v>
       </c>
     </row>
     <row r="99">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.16821575164795</v>
+        <v>29.00229835510254</v>
       </c>
     </row>
     <row r="100">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>19.98171997070312</v>
+        <v>8.354592323303223</v>
       </c>
     </row>
     <row r="101">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>7.110930919647217</v>
       </c>
     </row>
     <row r="102">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>21.8470573425293</v>
+        <v>7.958292484283447</v>
       </c>
     </row>
     <row r="103">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>129.7935791015625</v>
+        <v>97.09485626220703</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>300.7712097167969</v>
+        <v>198.2298431396484</v>
       </c>
     </row>
     <row r="105">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>633.59912109375</v>
+        <v>226.8204650878906</v>
       </c>
     </row>
     <row r="106">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>530.9395141601562</v>
+        <v>156.7997741699219</v>
       </c>
     </row>
     <row r="107">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>475.2144470214844</v>
+        <v>191.8067932128906</v>
       </c>
     </row>
     <row r="108">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>498.92529296875</v>
+        <v>170.3358001708984</v>
       </c>
     </row>
     <row r="109">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>808.4459228515625</v>
+        <v>221.6913604736328</v>
       </c>
     </row>
     <row r="110">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>928.0817260742188</v>
+        <v>184.80712890625</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>732.9078369140625</v>
+        <v>126.5654983520508</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>663.8118896484375</v>
+        <v>209.8729553222656</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>740.76025390625</v>
+        <v>52.93939971923828</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1030.012084960938</v>
+        <v>197.5241851806641</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1540.460083007812</v>
+        <v>214.1613464355469</v>
       </c>
     </row>
     <row r="116">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1422.883422851562</v>
+        <v>70.13622283935547</v>
       </c>
     </row>
     <row r="117">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1268.928955078125</v>
+        <v>41.32825469970703</v>
       </c>
     </row>
     <row r="118">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>864.267578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>511.0688171386719</v>
+        <v>11.22348594665527</v>
       </c>
     </row>
     <row r="120">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>328.7568054199219</v>
+        <v>4.990219593048096</v>
       </c>
     </row>
     <row r="121">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>137.6259460449219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>89.50759124755859</v>
+        <v>91.25881195068359</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>12.76919555664062</v>
+        <v>54.63921356201172</v>
       </c>
     </row>
     <row r="124">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>36.62046051025391</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>31.01762771606445</v>
       </c>
     </row>
     <row r="126">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>20.82988166809082</v>
       </c>
     </row>
     <row r="127">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>77.44483184814453</v>
+        <v>115.9667587280273</v>
       </c>
     </row>
     <row r="128">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>211.4763336181641</v>
+        <v>214.1215972900391</v>
       </c>
     </row>
     <row r="129">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>332.4071350097656</v>
+        <v>223.6227264404297</v>
       </c>
     </row>
     <row r="130">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>469.3248901367188</v>
+        <v>210.6649017333984</v>
       </c>
     </row>
     <row r="131">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>538.61962890625</v>
+        <v>234.4518127441406</v>
       </c>
     </row>
     <row r="132">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>670.7471923828125</v>
+        <v>237.3331909179688</v>
       </c>
     </row>
     <row r="133">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>763.1935424804688</v>
+        <v>234.7080841064453</v>
       </c>
     </row>
     <row r="134">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>893.9937744140625</v>
+        <v>272.9317626953125</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1006.739868164062</v>
+        <v>187.3390960693359</v>
       </c>
     </row>
     <row r="136">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1136.09228515625</v>
+        <v>253.3988800048828</v>
       </c>
     </row>
     <row r="137">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>978.64892578125</v>
+        <v>78.9259033203125</v>
       </c>
     </row>
     <row r="138">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>860.6063842773438</v>
+        <v>176.8258361816406</v>
       </c>
     </row>
     <row r="139">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>815.4059448242188</v>
+        <v>102.0212326049805</v>
       </c>
     </row>
     <row r="140">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>658.0527954101562</v>
+        <v>98.40201568603516</v>
       </c>
     </row>
     <row r="141">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>543.333984375</v>
+        <v>67.63255310058594</v>
       </c>
     </row>
     <row r="142">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>437.7706298828125</v>
+        <v>15.0575704574585</v>
       </c>
     </row>
     <row r="143">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>338.1376342773438</v>
+        <v>39.48926544189453</v>
       </c>
     </row>
     <row r="144">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>229.3237609863281</v>
+        <v>33.25603485107422</v>
       </c>
     </row>
     <row r="145">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>98.32124328613281</v>
+        <v>24.63466262817383</v>
       </c>
     </row>
     <row r="146">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>190.4814453125</v>
+        <v>90.56917572021484</v>
       </c>
     </row>
     <row r="147">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>164.1617584228516</v>
+        <v>62.71119689941406</v>
       </c>
     </row>
     <row r="148">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>89.62890625</v>
+        <v>42.4800910949707</v>
       </c>
     </row>
     <row r="149">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>105.0044708251953</v>
+        <v>42.98527526855469</v>
       </c>
     </row>
     <row r="150">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>52.33873748779297</v>
+        <v>38.62979507446289</v>
       </c>
     </row>
     <row r="151">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>312.791015625</v>
+        <v>143.2204132080078</v>
       </c>
     </row>
     <row r="152">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>526.8363037109375</v>
+        <v>252.3415374755859</v>
       </c>
     </row>
     <row r="153">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>955.0235595703125</v>
+        <v>256.3804626464844</v>
       </c>
     </row>
     <row r="154">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>840.1057739257812</v>
+        <v>176.8167114257812</v>
       </c>
     </row>
     <row r="155">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>753.2940063476562</v>
+        <v>233.7330474853516</v>
       </c>
     </row>
     <row r="156">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>836.8286743164062</v>
+        <v>182.0670776367188</v>
       </c>
     </row>
     <row r="157">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1142.714965820312</v>
+        <v>264.5072631835938</v>
       </c>
     </row>
     <row r="158">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1348.0859375</v>
+        <v>209.2861633300781</v>
       </c>
     </row>
     <row r="159">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1011.880065917969</v>
+        <v>150.7274169921875</v>
       </c>
     </row>
     <row r="160">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>916.6608276367188</v>
+        <v>242.9825286865234</v>
       </c>
     </row>
     <row r="161">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>881.9615478515625</v>
+        <v>97.54146575927734</v>
       </c>
     </row>
     <row r="162">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1266.689819335938</v>
+        <v>253.0549163818359</v>
       </c>
     </row>
     <row r="163">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1962.439331054688</v>
+        <v>245.6811370849609</v>
       </c>
     </row>
     <row r="164">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1794.781372070312</v>
+        <v>106.3414154052734</v>
       </c>
     </row>
     <row r="165">
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1601.435668945312</v>
+        <v>74.59880065917969</v>
       </c>
     </row>
     <row r="166">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1228.378540039062</v>
+        <v>51.17644500732422</v>
       </c>
     </row>
     <row r="167">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>804.6975708007812</v>
+        <v>53.34446334838867</v>
       </c>
     </row>
     <row r="168">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>560.5031127929688</v>
+        <v>37.26594924926758</v>
       </c>
     </row>
     <row r="169">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>377.5926513671875</v>
+        <v>35.5529670715332</v>
       </c>
     </row>
     <row r="170">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>169.2385711669922</v>
+        <v>128.2353363037109</v>
       </c>
     </row>
     <row r="171">
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>142.6133117675781</v>
+        <v>88.53206634521484</v>
       </c>
     </row>
     <row r="172">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>55.50594329833984</v>
+        <v>72.82962036132812</v>
       </c>
     </row>
     <row r="173">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>43.22738265991211</v>
+        <v>69.97084045410156</v>
       </c>
     </row>
     <row r="174">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>13.27409744262695</v>
+        <v>54.01980590820312</v>
       </c>
     </row>
     <row r="175">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>228.0187683105469</v>
+        <v>160.0332946777344</v>
       </c>
     </row>
     <row r="176">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>353.5078735351562</v>
+        <v>271.1751098632812</v>
       </c>
     </row>
     <row r="177">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>618.2838134765625</v>
+        <v>255.2664642333984</v>
       </c>
     </row>
     <row r="178">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>715.0857543945312</v>
+        <v>232.7653961181641</v>
       </c>
     </row>
     <row r="179">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>777.0139770507812</v>
+        <v>282.4505920410156</v>
       </c>
     </row>
     <row r="180">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>937.9297485351562</v>
+        <v>247.9796447753906</v>
       </c>
     </row>
     <row r="181">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1034.455078125</v>
+        <v>283.9029541015625</v>
       </c>
     </row>
     <row r="182">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1343.2880859375</v>
+        <v>294.4512023925781</v>
       </c>
     </row>
     <row r="183">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1265.782470703125</v>
+        <v>211.3210906982422</v>
       </c>
     </row>
     <row r="184">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1381.43896484375</v>
+        <v>291.7019653320312</v>
       </c>
     </row>
     <row r="185">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1249.111450195312</v>
+        <v>125.6115646362305</v>
       </c>
     </row>
     <row r="186">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1117.231079101562</v>
+        <v>234.4402313232422</v>
       </c>
     </row>
     <row r="187">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1021.887573242188</v>
+        <v>119.3237915039062</v>
       </c>
     </row>
     <row r="188">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>938.046142578125</v>
+        <v>136.6907348632812</v>
       </c>
     </row>
     <row r="189">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>802.5509033203125</v>
+        <v>102.9867095947266</v>
       </c>
     </row>
     <row r="190">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>683.2506713867188</v>
+        <v>80.19303131103516</v>
       </c>
     </row>
     <row r="191">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>594.862060546875</v>
+        <v>83.69395446777344</v>
       </c>
     </row>
     <row r="192">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>428.513427734375</v>
+        <v>67.61547088623047</v>
       </c>
     </row>
     <row r="193">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>316.9683532714844</v>
+        <v>67.33102416992188</v>
       </c>
     </row>
     <row r="194">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>61.06440734863281</v>
+        <v>59.75513458251953</v>
       </c>
     </row>
     <row r="195">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>9.614371299743652</v>
+        <v>32.68937683105469</v>
       </c>
     </row>
     <row r="196">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>12.43350696563721</v>
       </c>
     </row>
     <row r="197">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>11.15525817871094</v>
       </c>
     </row>
     <row r="198">
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>10.82758140563965</v>
       </c>
     </row>
     <row r="199">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>162.8407745361328</v>
+        <v>101.1210250854492</v>
       </c>
     </row>
     <row r="200">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>268.6214904785156</v>
+        <v>182.5142517089844</v>
       </c>
     </row>
     <row r="201">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>516.7501220703125</v>
+        <v>212.994873046875</v>
       </c>
     </row>
     <row r="202">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>492.0186767578125</v>
+        <v>168.0523071289062</v>
       </c>
     </row>
     <row r="203">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>520.8056640625</v>
+        <v>237.6784362792969</v>
       </c>
     </row>
     <row r="204">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>692.28857421875</v>
+        <v>188.8164672851562</v>
       </c>
     </row>
     <row r="205">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>734.7994995117188</v>
+        <v>236.22607421875</v>
       </c>
     </row>
     <row r="206">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>851.5337524414062</v>
+        <v>190.6259613037109</v>
       </c>
     </row>
     <row r="207">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>754.8582763671875</v>
+        <v>130.6444244384766</v>
       </c>
     </row>
     <row r="208">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>906.8838500976562</v>
+        <v>203.2953186035156</v>
       </c>
     </row>
     <row r="209">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>824.3517456054688</v>
+        <v>65.97593688964844</v>
       </c>
     </row>
     <row r="210">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>847.2244873046875</v>
+        <v>143.8938598632812</v>
       </c>
     </row>
     <row r="211">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1158.270874023438</v>
+        <v>221.1731567382812</v>
       </c>
     </row>
     <row r="212">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1488.936401367188</v>
+        <v>83.46800231933594</v>
       </c>
     </row>
     <row r="213">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1300.235473632812</v>
+        <v>21.88727378845215</v>
       </c>
     </row>
     <row r="214">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>921.65380859375</v>
+        <v>5.443427562713623</v>
       </c>
     </row>
     <row r="215">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>559.0494995117188</v>
+        <v>16.77605819702148</v>
       </c>
     </row>
     <row r="216">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>371.0513610839844</v>
+        <v>9.069125175476074</v>
       </c>
     </row>
     <row r="217">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>171.9509735107422</v>
+        <v>0.6961072683334351</v>
       </c>
     </row>
     <row r="218">
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>180.30224609375</v>
+        <v>95.99855804443359</v>
       </c>
     </row>
     <row r="219">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>117.0124053955078</v>
+        <v>60.28057479858398</v>
       </c>
     </row>
     <row r="220">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>46.65543365478516</v>
+        <v>42.65361404418945</v>
       </c>
     </row>
     <row r="221">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>46.79306411743164</v>
+        <v>37.01620483398438</v>
       </c>
     </row>
     <row r="222">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>50.44354629516602</v>
+        <v>26.08825492858887</v>
       </c>
     </row>
     <row r="223">
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>220.2517547607422</v>
+        <v>130.0246429443359</v>
       </c>
     </row>
     <row r="224">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>332.7630310058594</v>
+        <v>201.5351104736328</v>
       </c>
     </row>
     <row r="225">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>547.3782958984375</v>
+        <v>216.0898132324219</v>
       </c>
     </row>
     <row r="226">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>675.9136352539062</v>
+        <v>225.2266082763672</v>
       </c>
     </row>
     <row r="227">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1038.808837890625</v>
+        <v>283.1046142578125</v>
       </c>
     </row>
     <row r="228">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1369.034912109375</v>
+        <v>254.7403869628906</v>
       </c>
     </row>
     <row r="229">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>939.0513305664062</v>
+        <v>257.5324096679688</v>
       </c>
     </row>
     <row r="230">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1783.058837890625</v>
+        <v>277.1789855957031</v>
       </c>
     </row>
     <row r="231">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1633.621826171875</v>
+        <v>191.9575347900391</v>
       </c>
     </row>
     <row r="232">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1537.153564453125</v>
+        <v>241.8567352294922</v>
       </c>
     </row>
     <row r="233">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1429.672119140625</v>
+        <v>93.91670227050781</v>
       </c>
     </row>
     <row r="234">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>871.8947143554688</v>
+        <v>133.2965545654297</v>
       </c>
     </row>
     <row r="235">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1121.43359375</v>
+        <v>118.6913986206055</v>
       </c>
     </row>
     <row r="236">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1059.190307617188</v>
+        <v>113.6880874633789</v>
       </c>
     </row>
     <row r="237">
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>712.6161499023438</v>
+        <v>52.10729598999023</v>
       </c>
     </row>
     <row r="238">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>635.2013549804688</v>
+        <v>34.33056259155273</v>
       </c>
     </row>
     <row r="239">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>532.7905883789062</v>
+        <v>46.99609756469727</v>
       </c>
     </row>
     <row r="240">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>402.7369689941406</v>
+        <v>39.2891960144043</v>
       </c>
     </row>
     <row r="241">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>265.5565185546875</v>
+        <v>32.34474945068359</v>
       </c>
     </row>
     <row r="242">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>163.4900970458984</v>
+        <v>69.82172393798828</v>
       </c>
     </row>
     <row r="243">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>134.5301208496094</v>
+        <v>42.25304794311523</v>
       </c>
     </row>
     <row r="244">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>93.62429809570312</v>
+        <v>21.73268699645996</v>
       </c>
     </row>
     <row r="245">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>41.43425369262695</v>
+        <v>19.62366104125977</v>
       </c>
     </row>
     <row r="246">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>72.33857727050781</v>
+        <v>19.49741172790527</v>
       </c>
     </row>
     <row r="247">
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>239.3206176757812</v>
+        <v>118.7625503540039</v>
       </c>
     </row>
     <row r="248">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>493.2087097167969</v>
+        <v>234.2254180908203</v>
       </c>
     </row>
     <row r="249">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>865.5845947265625</v>
+        <v>203.1591796875</v>
       </c>
     </row>
     <row r="250">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>788.6878051757812</v>
+        <v>174.2462921142578</v>
       </c>
     </row>
     <row r="251">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>721.8524780273438</v>
+        <v>216.5462799072266</v>
       </c>
     </row>
     <row r="252">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>735.6097412109375</v>
+        <v>164.4015655517578</v>
       </c>
     </row>
     <row r="253">
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1058.91357421875</v>
+        <v>247.9416656494141</v>
       </c>
     </row>
     <row r="254">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1248.475341796875</v>
+        <v>184.0544281005859</v>
       </c>
     </row>
     <row r="255">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>967.9675903320312</v>
+        <v>144.1386413574219</v>
       </c>
     </row>
     <row r="256">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>847.5496826171875</v>
+        <v>210.6431884765625</v>
       </c>
     </row>
     <row r="257">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>847.84033203125</v>
+        <v>80.23541259765625</v>
       </c>
     </row>
     <row r="258">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1375.031982421875</v>
+        <v>227.5323944091797</v>
       </c>
     </row>
     <row r="259">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1758.646606445312</v>
+        <v>188.2097625732422</v>
       </c>
     </row>
     <row r="260">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1754.4873046875</v>
+        <v>82.51795959472656</v>
       </c>
     </row>
     <row r="261">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1533.577514648438</v>
+        <v>44.19339752197266</v>
       </c>
     </row>
     <row r="262">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1193.140747070312</v>
+        <v>39.71273422241211</v>
       </c>
     </row>
     <row r="263">
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>729.6178588867188</v>
+        <v>26.92765045166016</v>
       </c>
     </row>
     <row r="264">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>487.6026000976562</v>
+        <v>15.1434440612793</v>
       </c>
     </row>
     <row r="265">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>346.1383666992188</v>
+        <v>3.208868265151978</v>
       </c>
     </row>
     <row r="266">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>87.49187469482422</v>
+        <v>102.2370452880859</v>
       </c>
     </row>
     <row r="267">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>57.43343353271484</v>
+        <v>66.01619720458984</v>
       </c>
     </row>
     <row r="268">
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>5.889823913574219</v>
+        <v>48.12469863891602</v>
       </c>
     </row>
     <row r="269">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>0</v>
+        <v>42.65169143676758</v>
       </c>
     </row>
     <row r="270">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0</v>
+        <v>30.92998886108398</v>
       </c>
     </row>
     <row r="271">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>112.8552474975586</v>
+        <v>128.20361328125</v>
       </c>
     </row>
     <row r="272">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>294.0484924316406</v>
+        <v>250.2763519287109</v>
       </c>
     </row>
     <row r="273">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>531.6314697265625</v>
+        <v>207.5318298339844</v>
       </c>
     </row>
     <row r="274">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>627.2855834960938</v>
+        <v>227.5924682617188</v>
       </c>
     </row>
     <row r="275">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>677.4890747070312</v>
+        <v>256.12109375</v>
       </c>
     </row>
     <row r="276">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>784.359375</v>
+        <v>226.3566131591797</v>
       </c>
     </row>
     <row r="277">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>916.8143920898438</v>
+        <v>263.3795471191406</v>
       </c>
     </row>
     <row r="278">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1038.01611328125</v>
+        <v>266.1549682617188</v>
       </c>
     </row>
     <row r="279">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1174.406494140625</v>
+        <v>202.1679840087891</v>
       </c>
     </row>
     <row r="280">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1251.730346679688</v>
+        <v>247.8726043701172</v>
       </c>
     </row>
     <row r="281">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1133.070678710938</v>
+        <v>104.3480758666992</v>
       </c>
     </row>
     <row r="282">
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1063.59521484375</v>
+        <v>205.9118957519531</v>
       </c>
     </row>
     <row r="283">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>879.010009765625</v>
+        <v>88.04341888427734</v>
       </c>
     </row>
     <row r="284">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>947.2247314453125</v>
+        <v>108.9099426269531</v>
       </c>
     </row>
     <row r="285">
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>669.758544921875</v>
+        <v>68.62387847900391</v>
       </c>
     </row>
     <row r="286">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>608.0829467773438</v>
+        <v>64.77184295654297</v>
       </c>
     </row>
     <row r="287">
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>476.5518798828125</v>
+        <v>53.31959533691406</v>
       </c>
     </row>
     <row r="288">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>300.4497375488281</v>
+        <v>41.53541946411133</v>
       </c>
     </row>
     <row r="289">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>230.778564453125</v>
+        <v>31.02944564819336</v>
       </c>
     </row>
     <row r="290">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>43.92449951171875</v>
+        <v>28.62493705749512</v>
       </c>
     </row>
     <row r="291">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>3.122797012329102</v>
+        <v>3.378762483596802</v>
       </c>
     </row>
     <row r="292">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0</v>
+        <v>11.33221244812012</v>
       </c>
     </row>
     <row r="293">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>3.196584224700928</v>
       </c>
     </row>
     <row r="294">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>8.470339775085449</v>
+        <v>10.14678287506104</v>
       </c>
     </row>
     <row r="295">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>96.04621124267578</v>
+        <v>69.04907989501953</v>
       </c>
     </row>
     <row r="296">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>162.1059875488281</v>
+        <v>151.3190765380859</v>
       </c>
     </row>
     <row r="297">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>315.0759887695312</v>
+        <v>190.8694610595703</v>
       </c>
     </row>
     <row r="298">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>264.2450256347656</v>
+        <v>138.3065490722656</v>
       </c>
     </row>
     <row r="299">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>331.4157104492188</v>
+        <v>216.0868682861328</v>
       </c>
     </row>
     <row r="300">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>402.85400390625</v>
+        <v>149.9762115478516</v>
       </c>
     </row>
     <row r="301">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>514.287109375</v>
+        <v>127.7175903320312</v>
       </c>
     </row>
     <row r="302">
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>545.6409301757812</v>
+        <v>120.0029602050781</v>
       </c>
     </row>
     <row r="303">
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>465.3494567871094</v>
+        <v>48.30732727050781</v>
       </c>
     </row>
     <row r="304">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>396.4306335449219</v>
+        <v>66.76361846923828</v>
       </c>
     </row>
     <row r="305">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>345.6172485351562</v>
+        <v>36.61049652099609</v>
       </c>
     </row>
     <row r="306">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>534.9185791015625</v>
+        <v>79.16947174072266</v>
       </c>
     </row>
     <row r="307">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>735.4651489257812</v>
+        <v>206.3406982421875</v>
       </c>
     </row>
     <row r="308">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>592.4342651367188</v>
+        <v>44.73667526245117</v>
       </c>
     </row>
     <row r="309">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>507.7408447265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>384.4525451660156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>265.9161682128906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>175.8888854980469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>64.19258880615234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>26.20329093933105</v>
+        <v>49.92050933837891</v>
       </c>
     </row>
     <row r="315">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0</v>
+        <v>14.50371170043945</v>
       </c>
     </row>
     <row r="316">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0</v>
+        <v>26.6044979095459</v>
       </c>
     </row>
     <row r="317">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>0</v>
+        <v>14.10975551605225</v>
       </c>
     </row>
     <row r="318">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>0</v>
+        <v>10.45959186553955</v>
       </c>
     </row>
     <row r="319">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>62.70013809204102</v>
+        <v>83.00490570068359</v>
       </c>
     </row>
     <row r="320">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>130.6709594726562</v>
+        <v>155.3919982910156</v>
       </c>
     </row>
     <row r="321">
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>269.5731506347656</v>
+        <v>188.4606475830078</v>
       </c>
     </row>
     <row r="322">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>397.9151000976562</v>
+        <v>180.5328979492188</v>
       </c>
     </row>
     <row r="323">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>568.6531372070312</v>
+        <v>245.369140625</v>
       </c>
     </row>
     <row r="324">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>681.4241333007812</v>
+        <v>200.9523010253906</v>
       </c>
     </row>
     <row r="325">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>783.6397705078125</v>
+        <v>134.0759582519531</v>
       </c>
     </row>
     <row r="326">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>886.3059692382812</v>
+        <v>190.010009765625</v>
       </c>
     </row>
     <row r="327">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>894.250244140625</v>
+        <v>96.06558227539062</v>
       </c>
     </row>
     <row r="328">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>701.5167846679688</v>
+        <v>92.09075927734375</v>
       </c>
     </row>
     <row r="329">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>577.4693603515625</v>
+        <v>49.60345077514648</v>
       </c>
     </row>
     <row r="330">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>472.8200988769531</v>
+        <v>53.62430572509766</v>
       </c>
     </row>
     <row r="331">
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>386.1719970703125</v>
+        <v>81.62644958496094</v>
       </c>
     </row>
     <row r="332">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>333.9766235351562</v>
+        <v>60.00893783569336</v>
       </c>
     </row>
     <row r="333">
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>261.2723388671875</v>
+        <v>11.16781711578369</v>
       </c>
     </row>
     <row r="334">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>213.3694458007812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>136.0341949462891</v>
+        <v>14.52657127380371</v>
       </c>
     </row>
     <row r="336">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>84.35896301269531</v>
+        <v>4.039443492889404</v>
       </c>
     </row>
     <row r="337">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>10.58631610870361</v>
+        <v>4.425427436828613</v>
       </c>
     </row>
     <row r="338">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>30.75417900085449</v>
+        <v>30.50230598449707</v>
       </c>
     </row>
     <row r="339">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>2.095701217651367</v>
+        <v>5.256124973297119</v>
       </c>
     </row>
     <row r="340">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>20.15014457702637</v>
+        <v>13.20957088470459</v>
       </c>
     </row>
     <row r="341">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>16.62956619262695</v>
+        <v>5.07394552230835</v>
       </c>
     </row>
     <row r="342">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>16.00094032287598</v>
+        <v>12.02413940429688</v>
       </c>
     </row>
     <row r="343">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>85.77326202392578</v>
+        <v>70.05077362060547</v>
       </c>
     </row>
     <row r="344">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>220.3495635986328</v>
+        <v>157.8410491943359</v>
       </c>
     </row>
     <row r="345">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>454.9967346191406</v>
+        <v>195.5510711669922</v>
       </c>
     </row>
     <row r="346">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>583.3314819335938</v>
+        <v>145.3343658447266</v>
       </c>
     </row>
     <row r="347">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>694.106201171875</v>
+        <v>210.6373748779297</v>
       </c>
     </row>
     <row r="348">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>680.3637084960938</v>
+        <v>149.3174438476562</v>
       </c>
     </row>
     <row r="349">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>616.647216796875</v>
+        <v>129.2042541503906</v>
       </c>
     </row>
     <row r="350">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>514.2874145507812</v>
+        <v>119.5856323242188</v>
       </c>
     </row>
     <row r="351">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>481.9961547851562</v>
+        <v>50.18468856811523</v>
       </c>
     </row>
     <row r="352">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>356.4455871582031</v>
+        <v>67.82908630371094</v>
       </c>
     </row>
     <row r="353">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>424.7149047851562</v>
+        <v>38.48786163330078</v>
       </c>
     </row>
     <row r="354">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>655.4287109375</v>
+        <v>84.21871948242188</v>
       </c>
     </row>
     <row r="355">
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>968.2640380859375</v>
+        <v>216.0745391845703</v>
       </c>
     </row>
     <row r="356">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>860.348388671875</v>
+        <v>46.61403656005859</v>
       </c>
     </row>
     <row r="357">
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>629.1663818359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>481.179931640625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>332.8985595703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>202.5798034667969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>70.15115356445312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>0</v>
+        <v>49.84359359741211</v>
       </c>
     </row>
     <row r="363">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0</v>
+        <v>14.42679977416992</v>
       </c>
     </row>
     <row r="364">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0</v>
+        <v>26.52758979797363</v>
       </c>
     </row>
     <row r="365">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>0</v>
+        <v>14.03284358978271</v>
       </c>
     </row>
     <row r="366">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>0</v>
+        <v>10.38268184661865</v>
       </c>
     </row>
     <row r="367">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>0</v>
+        <v>82.05233764648438</v>
       </c>
     </row>
     <row r="368">
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>68.90486907958984</v>
+        <v>159.9596862792969</v>
       </c>
     </row>
     <row r="369">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>215.3537902832031</v>
+        <v>191.1879730224609</v>
       </c>
     </row>
     <row r="370">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>403.98974609375</v>
+        <v>185.6064453125</v>
       </c>
     </row>
     <row r="371">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>538.8673095703125</v>
+        <v>237.9653625488281</v>
       </c>
     </row>
     <row r="372">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>623.6492309570312</v>
+        <v>198.3392486572266</v>
       </c>
     </row>
     <row r="373">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>706.6126098632812</v>
+        <v>133.6083526611328</v>
       </c>
     </row>
     <row r="374">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>594.4447631835938</v>
+        <v>187.6384124755859</v>
       </c>
     </row>
     <row r="375">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1135.307739257812</v>
+        <v>97.40336608886719</v>
       </c>
     </row>
     <row r="376">
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>486.3776245117188</v>
+        <v>91.20193481445312</v>
       </c>
     </row>
     <row r="377">
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>441.7636413574219</v>
+        <v>49.52653503417969</v>
       </c>
     </row>
     <row r="378">
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>313.7788391113281</v>
+        <v>56.71927642822266</v>
       </c>
     </row>
     <row r="379">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>387.4386291503906</v>
+        <v>89.406005859375</v>
       </c>
     </row>
     <row r="380">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>484.2936096191406</v>
+        <v>59.93202590942383</v>
       </c>
     </row>
     <row r="381">
@@ -6527,7 +6527,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>294.841552734375</v>
+        <v>11.09090518951416</v>
       </c>
     </row>
     <row r="382">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>196.2834625244141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>115.6344528198242</v>
+        <v>12.58750057220459</v>
       </c>
     </row>
     <row r="384">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>34.13418960571289</v>
+        <v>3.96253228187561</v>
       </c>
     </row>
     <row r="385">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>0</v>
+        <v>4.348516941070557</v>
       </c>
     </row>
     <row r="386">
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>93.51823425292969</v>
+        <v>28.62493705749512</v>
       </c>
     </row>
     <row r="387">
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>4.612496852874756</v>
+        <v>3.378762483596802</v>
       </c>
     </row>
     <row r="388">
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>11.33221244812012</v>
       </c>
     </row>
     <row r="389">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>114.5692443847656</v>
+        <v>3.196584224700928</v>
       </c>
     </row>
     <row r="390">
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>6.51150369644165</v>
+        <v>10.14678287506104</v>
       </c>
     </row>
     <row r="391">
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>103.7228088378906</v>
+        <v>69.04907989501953</v>
       </c>
     </row>
     <row r="392">
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>190.9814910888672</v>
+        <v>151.3190765380859</v>
       </c>
     </row>
     <row r="393">
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>423.0182800292969</v>
+        <v>190.8694610595703</v>
       </c>
     </row>
     <row r="394">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>387.2612915039062</v>
+        <v>138.3065490722656</v>
       </c>
     </row>
     <row r="395">
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>505.6578369140625</v>
+        <v>216.0868682861328</v>
       </c>
     </row>
     <row r="396">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>474.6695556640625</v>
+        <v>149.9762115478516</v>
       </c>
     </row>
     <row r="397">
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>675.9583129882812</v>
+        <v>127.7175903320312</v>
       </c>
     </row>
     <row r="398">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>827.5731201171875</v>
+        <v>120.0029602050781</v>
       </c>
     </row>
     <row r="399">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>980.2925415039062</v>
+        <v>48.30732727050781</v>
       </c>
     </row>
     <row r="400">
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>823.6653442382812</v>
+        <v>66.76361846923828</v>
       </c>
     </row>
     <row r="401">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>919.5048828125</v>
+        <v>36.61049652099609</v>
       </c>
     </row>
     <row r="402">
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>842.9017333984375</v>
+        <v>79.16947174072266</v>
       </c>
     </row>
     <row r="403">
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>957.2096557617188</v>
+        <v>206.3406982421875</v>
       </c>
     </row>
     <row r="404">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1161.45166015625</v>
+        <v>44.73667526245117</v>
       </c>
     </row>
     <row r="405">
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>1026.495727539062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>505.0263977050781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>442.9168395996094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>294.5220336914062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>122.5602645874023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>522.9031372070312</v>
+        <v>49.92050933837891</v>
       </c>
     </row>
     <row r="411">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>168.7071685791016</v>
+        <v>14.50371170043945</v>
       </c>
     </row>
     <row r="412">
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>119.1724166870117</v>
+        <v>26.6044979095459</v>
       </c>
     </row>
     <row r="413">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>510.8319702148438</v>
+        <v>14.10975551605225</v>
       </c>
     </row>
     <row r="414">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>44.59515762329102</v>
+        <v>10.45959186553955</v>
       </c>
     </row>
     <row r="415">
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>278.430908203125</v>
+        <v>83.00490570068359</v>
       </c>
     </row>
     <row r="416">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>450.5870971679688</v>
+        <v>155.3919982910156</v>
       </c>
     </row>
     <row r="417">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>733.3729248046875</v>
+        <v>188.4606475830078</v>
       </c>
     </row>
     <row r="418">
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>1021.342956542969</v>
+        <v>180.5328979492188</v>
       </c>
     </row>
     <row r="419">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1416.80859375</v>
+        <v>245.369140625</v>
       </c>
     </row>
     <row r="420">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1029.168212890625</v>
+        <v>200.9523010253906</v>
       </c>
     </row>
     <row r="421">
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>2026.050048828125</v>
+        <v>134.0759582519531</v>
       </c>
     </row>
     <row r="422">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>2213.71337890625</v>
+        <v>190.010009765625</v>
       </c>
     </row>
     <row r="423">
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>2092.690185546875</v>
+        <v>96.06558227539062</v>
       </c>
     </row>
     <row r="424">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>1258.086669921875</v>
+        <v>92.09075927734375</v>
       </c>
     </row>
     <row r="425">
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1756.18505859375</v>
+        <v>49.60345077514648</v>
       </c>
     </row>
     <row r="426">
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>1479.992553710938</v>
+        <v>53.62430572509766</v>
       </c>
     </row>
     <row r="427">
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>931.4163208007812</v>
+        <v>81.62644958496094</v>
       </c>
     </row>
     <row r="428">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1105.397705078125</v>
+        <v>60.00893783569336</v>
       </c>
     </row>
     <row r="429">
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>931.3079223632812</v>
+        <v>11.16781711578369</v>
       </c>
     </row>
     <row r="430">
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>744.9276733398438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>539.1234741210938</v>
+        <v>14.52657127380371</v>
       </c>
     </row>
     <row r="432">
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>381.5194396972656</v>
+        <v>4.039443492889404</v>
       </c>
     </row>
     <row r="433">
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>212.5423583984375</v>
+        <v>4.425427436828613</v>
       </c>
     </row>
     <row r="434">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>53.43187713623047</v>
+        <v>25.80452156066895</v>
       </c>
     </row>
     <row r="435">
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>11.94244956970215</v>
+        <v>0.5583485960960388</v>
       </c>
     </row>
     <row r="436">
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>40.78215789794922</v>
+        <v>8.511796951293945</v>
       </c>
     </row>
     <row r="437">
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>29.44292831420898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>28.86112403869629</v>
+        <v>7.326359272003174</v>
       </c>
     </row>
     <row r="439">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>152.9564971923828</v>
+        <v>63.20829010009766</v>
       </c>
     </row>
     <row r="440">
@@ -7471,7 +7471,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>249.2915496826172</v>
+        <v>151.3801574707031</v>
       </c>
     </row>
     <row r="441">
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>417.1718139648438</v>
+        <v>184.0618133544922</v>
       </c>
     </row>
     <row r="442">
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>384.1197204589844</v>
+        <v>135.4861297607422</v>
       </c>
     </row>
     <row r="443">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>414.0970153808594</v>
+        <v>200.8737640380859</v>
       </c>
     </row>
     <row r="444">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>501.4454345703125</v>
+        <v>146.6589508056641</v>
       </c>
     </row>
     <row r="445">
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>625.9962158203125</v>
+        <v>127.564338684082</v>
       </c>
     </row>
     <row r="446">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>684.5767211914062</v>
+        <v>116.2087860107422</v>
       </c>
     </row>
     <row r="447">
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>533.4033203125</v>
+        <v>52.02325439453125</v>
       </c>
     </row>
     <row r="448">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>503.0964660644531</v>
+        <v>65.65677642822266</v>
       </c>
     </row>
     <row r="449">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>451.8672485351562</v>
+        <v>31.79120635986328</v>
       </c>
     </row>
     <row r="450">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>659.4552001953125</v>
+        <v>76.34906768798828</v>
       </c>
     </row>
     <row r="451">
@@ -7647,7 +7647,7 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>819.3598022460938</v>
+        <v>199.0410461425781</v>
       </c>
     </row>
     <row r="452">
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="D452" t="n">
-        <v>787.156494140625</v>
+        <v>41.91626358032227</v>
       </c>
     </row>
     <row r="453">
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>701.0865478515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>544.5576782226562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>366.1149291992188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456">
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>247.9904937744141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="457">
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>101.9395294189453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>59.14260864257812</v>
+        <v>47.10008239746094</v>
       </c>
     </row>
     <row r="459">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>0</v>
+        <v>11.6832971572876</v>
       </c>
     </row>
     <row r="460">
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>0</v>
+        <v>23.78407859802246</v>
       </c>
     </row>
     <row r="461">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>0</v>
+        <v>9.540475845336914</v>
       </c>
     </row>
     <row r="462">
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>0</v>
+        <v>7.63917875289917</v>
       </c>
     </row>
     <row r="463">
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>90.99609375</v>
+        <v>73.05048370361328</v>
       </c>
     </row>
     <row r="464">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>211.6399688720703</v>
+        <v>155.4530792236328</v>
       </c>
     </row>
     <row r="465">
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>353.9810791015625</v>
+        <v>181.6529998779297</v>
       </c>
     </row>
     <row r="466">
@@ -7887,7 +7887,7 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>458.6196899414062</v>
+        <v>177.7124633789062</v>
       </c>
     </row>
     <row r="467">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>606.1534423828125</v>
+        <v>230.1560668945312</v>
       </c>
     </row>
     <row r="468">
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>704.3707885742188</v>
+        <v>197.6351165771484</v>
       </c>
     </row>
     <row r="469">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>832.6787109375</v>
+        <v>133.9227142333984</v>
       </c>
     </row>
     <row r="470">
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>952.9539794921875</v>
+        <v>187.1896057128906</v>
       </c>
     </row>
     <row r="471">
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>952.4724731445312</v>
+        <v>99.781494140625</v>
       </c>
     </row>
     <row r="472">
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>780.5320434570312</v>
+        <v>89.27032470703125</v>
       </c>
     </row>
     <row r="473">
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>684.2241821289062</v>
+        <v>44.78416061401367</v>
       </c>
     </row>
     <row r="474">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>563.0699462890625</v>
+        <v>50.80387878417969</v>
       </c>
     </row>
     <row r="475">
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>435.1701965332031</v>
+        <v>71.09329223632812</v>
       </c>
     </row>
     <row r="476">
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>419.2275695800781</v>
+        <v>57.18851852416992</v>
       </c>
     </row>
     <row r="477">
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>341.151611328125</v>
+        <v>8.347383499145508</v>
       </c>
     </row>
     <row r="478">
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>333.2835998535156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>222.4372100830078</v>
+        <v>6.24294900894165</v>
       </c>
     </row>
     <row r="480">
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>163.2819213867188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>48.0498161315918</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/hourly_prediction.xlsx
+++ b/results/tables/hourly_prediction.xlsx
@@ -459,11 +459,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>81.34810638427734</v>
+        <v>126.7713851928711</v>
       </c>
     </row>
     <row r="3">
@@ -475,11 +475,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>53.49015808105469</v>
+        <v>120.0708312988281</v>
       </c>
     </row>
     <row r="4">
@@ -491,11 +491,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.25905227661133</v>
+        <v>72.84970092773438</v>
       </c>
     </row>
     <row r="5">
@@ -507,11 +507,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.015380859375</v>
+        <v>177.1533813476562</v>
       </c>
     </row>
     <row r="6">
@@ -523,11 +523,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.84358978271484</v>
+        <v>65.32220458984375</v>
       </c>
     </row>
     <row r="7">
@@ -539,11 +539,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>130.4363708496094</v>
+        <v>138.7206115722656</v>
       </c>
     </row>
     <row r="8">
@@ -555,11 +555,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>246.6989288330078</v>
+        <v>64.33561706542969</v>
       </c>
     </row>
     <row r="9">
@@ -571,11 +571,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>252.0441589355469</v>
+        <v>17.86163139343262</v>
       </c>
     </row>
     <row r="10">
@@ -587,11 +587,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>162.4486083984375</v>
+        <v>65.37339782714844</v>
       </c>
     </row>
     <row r="11">
@@ -603,11 +603,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>203.4707794189453</v>
+        <v>83.68783569335938</v>
       </c>
     </row>
     <row r="12">
@@ -619,11 +619,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>170.2646942138672</v>
+        <v>178.2192840576172</v>
       </c>
     </row>
     <row r="13">
@@ -635,11 +635,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>243.4815979003906</v>
+        <v>153.5719909667969</v>
       </c>
     </row>
     <row r="14">
@@ -651,11 +651,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>198.5749816894531</v>
+        <v>110.9929885864258</v>
       </c>
     </row>
     <row r="15">
@@ -667,11 +667,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>147.7231597900391</v>
+        <v>204.3344879150391</v>
       </c>
     </row>
     <row r="16">
@@ -683,11 +683,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>236.7548828125</v>
+        <v>108.3824996948242</v>
       </c>
     </row>
     <row r="17">
@@ -699,11 +699,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>84.80300140380859</v>
+        <v>127.9548950195312</v>
       </c>
     </row>
     <row r="18">
@@ -715,11 +715,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>245.98291015625</v>
+        <v>19.94508361816406</v>
       </c>
     </row>
     <row r="19">
@@ -731,11 +731,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>235.9208068847656</v>
+        <v>1.591109991073608</v>
       </c>
     </row>
     <row r="20">
@@ -747,11 +747,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>99.98149871826172</v>
+        <v>207.1872711181641</v>
       </c>
     </row>
     <row r="21">
@@ -763,11 +763,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67.92855072021484</v>
+        <v>92.08646392822266</v>
       </c>
     </row>
     <row r="22">
@@ -779,11 +779,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>23.0381965637207</v>
+        <v>79.34138488769531</v>
       </c>
     </row>
     <row r="23">
@@ -795,11 +795,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>38.66020202636719</v>
+        <v>55.11704635620117</v>
       </c>
     </row>
     <row r="24">
@@ -811,11 +811,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26.09228324890137</v>
+        <v>23.13222885131836</v>
       </c>
     </row>
     <row r="25">
@@ -827,11 +827,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.24177551269531</v>
+        <v>112.5208511352539</v>
       </c>
     </row>
     <row r="26">
@@ -843,11 +843,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>118.7700424194336</v>
+        <v>18.5197639465332</v>
       </c>
     </row>
     <row r="27">
@@ -859,11 +859,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>79.0667724609375</v>
+        <v>73.37750244140625</v>
       </c>
     </row>
     <row r="28">
@@ -875,11 +875,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63.36428833007812</v>
+        <v>10.37394714355469</v>
       </c>
     </row>
     <row r="29">
@@ -891,11 +891,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>58.75662994384766</v>
+        <v>8.204967498779297</v>
       </c>
     </row>
     <row r="30">
@@ -907,11 +907,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>44.55452346801758</v>
+        <v>24.31366157531738</v>
       </c>
     </row>
     <row r="31">
@@ -923,11 +923,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>142.8913879394531</v>
+        <v>24.39325904846191</v>
       </c>
     </row>
     <row r="32">
@@ -939,11 +939,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>265.2882995605469</v>
+        <v>135.4741668701172</v>
       </c>
     </row>
     <row r="33">
@@ -955,11 +955,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>250.6858367919922</v>
+        <v>85.32801818847656</v>
       </c>
     </row>
     <row r="34">
@@ -971,11 +971,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>216.195068359375</v>
+        <v>32.36785125732422</v>
       </c>
     </row>
     <row r="35">
@@ -987,11 +987,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>251.9441223144531</v>
+        <v>142.4788208007812</v>
       </c>
     </row>
     <row r="36">
@@ -1003,11 +1003,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>235.9330291748047</v>
+        <v>22.9101448059082</v>
       </c>
     </row>
     <row r="37">
@@ -1019,11 +1019,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>258.4597778320312</v>
+        <v>61.68816375732422</v>
       </c>
     </row>
     <row r="38">
@@ -1035,11 +1035,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>288.5391845703125</v>
+        <v>1.192378759384155</v>
       </c>
     </row>
     <row r="39">
@@ -1051,11 +1051,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>208.0726470947266</v>
+        <v>0.0503169521689415</v>
       </c>
     </row>
     <row r="40">
@@ -1067,11 +1067,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>283.5165710449219</v>
+        <v>73.65728759765625</v>
       </c>
     </row>
     <row r="41">
@@ -1083,11 +1083,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>112.6288681030273</v>
+        <v>20.48125839233398</v>
       </c>
     </row>
     <row r="42">
@@ -1099,11 +1099,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>227.1239776611328</v>
+        <v>59.89609146118164</v>
       </c>
     </row>
     <row r="43">
@@ -1115,11 +1115,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>106.0858001708984</v>
+        <v>35.37281799316406</v>
       </c>
     </row>
     <row r="44">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>130.086669921875</v>
+        <v>13.51363277435303</v>
       </c>
     </row>
     <row r="45">
@@ -1147,11 +1147,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>96.07222747802734</v>
+        <v>90.96039581298828</v>
       </c>
     </row>
     <row r="46">
@@ -1163,11 +1163,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>53.14333343505859</v>
+        <v>7.596230506896973</v>
       </c>
     </row>
     <row r="47">
@@ -1179,11 +1179,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>68.76545715332031</v>
+        <v>66.6220703125</v>
       </c>
     </row>
     <row r="48">
@@ -1195,11 +1195,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>56.19747543334961</v>
+        <v>8.902968406677246</v>
       </c>
     </row>
     <row r="49">
@@ -1211,11 +1211,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>49.77550506591797</v>
+        <v>12.26431465148926</v>
       </c>
     </row>
     <row r="50">
@@ -1227,11 +1227,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>68.90352630615234</v>
+        <v>16.3341121673584</v>
       </c>
     </row>
     <row r="51">
@@ -1243,11 +1243,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>41.94034194946289</v>
+        <v>20.22287750244141</v>
       </c>
     </row>
     <row r="52">
@@ -1259,11 +1259,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>21.58189964294434</v>
+        <v>64.92958068847656</v>
       </c>
     </row>
     <row r="53">
@@ -1275,11 +1275,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>20.33823013305664</v>
+        <v>29.13995170593262</v>
       </c>
     </row>
     <row r="54">
@@ -1291,11 +1291,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>20.95535850524902</v>
+        <v>4.666910171508789</v>
       </c>
     </row>
     <row r="55">
@@ -1307,11 +1307,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>119.0669326782227</v>
+        <v>68.81431579589844</v>
       </c>
     </row>
     <row r="56">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>212.9118347167969</v>
+        <v>1.335822105407715</v>
       </c>
     </row>
     <row r="57">
@@ -1339,11 +1339,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>240.3670043945312</v>
+        <v>19.76883888244629</v>
       </c>
     </row>
     <row r="58">
@@ -1355,11 +1355,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>165.1163940429688</v>
+        <v>0.05625011399388313</v>
       </c>
     </row>
     <row r="59">
@@ -1371,11 +1371,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>200.5235290527344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1387,11 +1387,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>176.0921936035156</v>
+        <v>16.07491683959961</v>
       </c>
     </row>
     <row r="61">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>233.9677276611328</v>
+        <v>2.379360675811768</v>
       </c>
     </row>
     <row r="62">
@@ -1419,11 +1419,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>187.7848663330078</v>
+        <v>35.39579772949219</v>
       </c>
     </row>
     <row r="63">
@@ -1435,11 +1435,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>137.34619140625</v>
+        <v>19.11402702331543</v>
       </c>
     </row>
     <row r="64">
@@ -1451,11 +1451,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>222.6149291992188</v>
+        <v>14.21615600585938</v>
       </c>
     </row>
     <row r="65">
@@ -1467,11 +1467,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>73.12583160400391</v>
+        <v>55.02458953857422</v>
       </c>
     </row>
     <row r="66">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>232.0908660888672</v>
+        <v>9.208283424377441</v>
       </c>
     </row>
     <row r="67">
@@ -1499,11 +1499,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>260.0937194824219</v>
+        <v>19.35184288024902</v>
       </c>
     </row>
     <row r="68">
@@ -1515,11 +1515,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>86.22464752197266</v>
+        <v>10.76240730285645</v>
       </c>
     </row>
     <row r="69">
@@ -1531,11 +1531,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>56.25133514404297</v>
+        <v>14.41924571990967</v>
       </c>
     </row>
     <row r="70">
@@ -1547,11 +1547,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>8.009797096252441</v>
       </c>
     </row>
     <row r="71">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>23.52226638793945</v>
+        <v>15.93400573730469</v>
       </c>
     </row>
     <row r="72">
@@ -1579,11 +1579,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>17.63997459411621</v>
+        <v>24.22258377075195</v>
       </c>
     </row>
     <row r="73">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8.690741539001465</v>
+        <v>6.140839576721191</v>
       </c>
     </row>
     <row r="74">
@@ -1611,11 +1611,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>104.4861068725586</v>
+        <v>3.150290489196777</v>
       </c>
     </row>
     <row r="75">
@@ -1627,11 +1627,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>65.67755126953125</v>
+        <v>21.33364105224609</v>
       </c>
     </row>
     <row r="76">
@@ -1643,11 +1643,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>49.84771347045898</v>
+        <v>0.1969220638275146</v>
       </c>
     </row>
     <row r="77">
@@ -1659,11 +1659,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>44.24488067626953</v>
+        <v>1.225827217102051</v>
       </c>
     </row>
     <row r="78">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>33.82689666748047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1691,11 +1691,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>129.6825866699219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1707,11 +1707,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>230.5915985107422</v>
+        <v>1.219763278961182</v>
       </c>
     </row>
     <row r="81">
@@ -1723,11 +1723,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>237.1692657470703</v>
+        <v>0.3083613514900208</v>
       </c>
     </row>
     <row r="82">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>218.9814910888672</v>
+        <v>19.84250640869141</v>
       </c>
     </row>
     <row r="83">
@@ -1755,11 +1755,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>247.1575164794922</v>
+        <v>31.27795028686523</v>
       </c>
     </row>
     <row r="84">
@@ -1771,11 +1771,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>243.0895843505859</v>
+        <v>19.10197448730469</v>
       </c>
     </row>
     <row r="85">
@@ -1787,11 +1787,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>245.4072113037109</v>
+        <v>20.27435302734375</v>
       </c>
     </row>
     <row r="86">
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>275.9095458984375</v>
+        <v>11.84677410125732</v>
       </c>
     </row>
     <row r="87">
@@ -1819,11 +1819,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>195.8562622070312</v>
+        <v>26.33778381347656</v>
       </c>
     </row>
     <row r="88">
@@ -1835,11 +1835,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>267.5370788574219</v>
+        <v>12.39741516113281</v>
       </c>
     </row>
     <row r="89">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>99.11233520507812</v>
+        <v>17.54273796081543</v>
       </c>
     </row>
     <row r="90">
@@ -1867,11 +1867,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>211.3925628662109</v>
+        <v>9.361972808837891</v>
       </c>
     </row>
     <row r="91">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>115.5783996582031</v>
+        <v>17.97896003723145</v>
       </c>
     </row>
     <row r="92">
@@ -1899,11 +1899,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>114.4904708862305</v>
+        <v>6.046728134155273</v>
       </c>
     </row>
     <row r="93">
@@ -1915,11 +1915,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>82.55567169189453</v>
+        <v>6.603084087371826</v>
       </c>
     </row>
     <row r="94">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>21.7487621307373</v>
+        <v>3.273776054382324</v>
       </c>
     </row>
     <row r="95">
@@ -1947,11 +1947,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>51.78805923461914</v>
+        <v>3.782121181488037</v>
       </c>
     </row>
     <row r="96">
@@ -1963,11 +1963,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>45.90579223632812</v>
+        <v>0.08214350789785385</v>
       </c>
     </row>
     <row r="97">
@@ -1979,11 +1979,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>38.38510513305664</v>
+        <v>0.7608871459960938</v>
       </c>
     </row>
     <row r="98">
@@ -1995,11 +1995,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>55.67623519897461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2011,11 +2011,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>29.00229835510254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2027,11 +2027,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8.354592323303223</v>
+        <v>0.5734118223190308</v>
       </c>
     </row>
     <row r="101">
@@ -2043,11 +2043,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>7.110930919647217</v>
+        <v>0.2961122393608093</v>
       </c>
     </row>
     <row r="102">
@@ -2059,11 +2059,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>7.958292484283447</v>
+        <v>201.5604705810547</v>
       </c>
     </row>
     <row r="103">
@@ -2075,11 +2075,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>97.09485626220703</v>
+        <v>234.0678405761719</v>
       </c>
     </row>
     <row r="104">
@@ -2091,11 +2091,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>198.2298431396484</v>
+        <v>122.2492218017578</v>
       </c>
     </row>
     <row r="105">
@@ -2107,11 +2107,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>226.8204650878906</v>
+        <v>280.9053955078125</v>
       </c>
     </row>
     <row r="106">
@@ -2123,11 +2123,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>156.7997741699219</v>
+        <v>138.8390502929688</v>
       </c>
     </row>
     <row r="107">
@@ -2139,11 +2139,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>191.8067932128906</v>
+        <v>234.1094360351562</v>
       </c>
     </row>
     <row r="108">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>170.3358001708984</v>
+        <v>108.1467437744141</v>
       </c>
     </row>
     <row r="109">
@@ -2171,11 +2171,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>221.6913604736328</v>
+        <v>105.9049224853516</v>
       </c>
     </row>
     <row r="110">
@@ -2187,11 +2187,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>184.80712890625</v>
+        <v>121.6353759765625</v>
       </c>
     </row>
     <row r="111">
@@ -2203,11 +2203,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>126.5654983520508</v>
+        <v>174.1945190429688</v>
       </c>
     </row>
     <row r="112">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>209.8729553222656</v>
+        <v>118.6570587158203</v>
       </c>
     </row>
     <row r="113">
@@ -2235,11 +2235,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>52.93939971923828</v>
+        <v>125.5331878662109</v>
       </c>
     </row>
     <row r="114">
@@ -2251,11 +2251,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>197.5241851806641</v>
+        <v>83.99700164794922</v>
       </c>
     </row>
     <row r="115">
@@ -2267,11 +2267,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>214.1613464355469</v>
+        <v>174.1988677978516</v>
       </c>
     </row>
     <row r="116">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>70.13622283935547</v>
+        <v>132.2134246826172</v>
       </c>
     </row>
     <row r="117">
@@ -2299,11 +2299,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>41.32825469970703</v>
+        <v>109.2806701660156</v>
       </c>
     </row>
     <row r="118">
@@ -2315,11 +2315,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>93.05605316162109</v>
       </c>
     </row>
     <row r="119">
@@ -2331,11 +2331,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.22348594665527</v>
+        <v>60.02500915527344</v>
       </c>
     </row>
     <row r="120">
@@ -2347,11 +2347,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4.990219593048096</v>
+        <v>179.8536376953125</v>
       </c>
     </row>
     <row r="121">
@@ -2363,11 +2363,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>107.4787139892578</v>
       </c>
     </row>
     <row r="122">
@@ -2379,11 +2379,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>91.25881195068359</v>
+        <v>467.0384826660156</v>
       </c>
     </row>
     <row r="123">
@@ -2395,11 +2395,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>54.63921356201172</v>
+        <v>472.629638671875</v>
       </c>
     </row>
     <row r="124">
@@ -2411,11 +2411,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>36.62046051025391</v>
+        <v>273.8912048339844</v>
       </c>
     </row>
     <row r="125">
@@ -2427,11 +2427,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>31.01762771606445</v>
+        <v>531.4622802734375</v>
       </c>
     </row>
     <row r="126">
@@ -2443,11 +2443,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>20.82988166809082</v>
+        <v>252.4641876220703</v>
       </c>
     </row>
     <row r="127">
@@ -2459,11 +2459,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>115.9667587280273</v>
+        <v>529.9881591796875</v>
       </c>
     </row>
     <row r="128">
@@ -2475,11 +2475,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>214.1215972900391</v>
+        <v>180.4799499511719</v>
       </c>
     </row>
     <row r="129">
@@ -2491,11 +2491,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>223.6227264404297</v>
+        <v>219.8799285888672</v>
       </c>
     </row>
     <row r="130">
@@ -2507,11 +2507,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>210.6649017333984</v>
+        <v>198.1952972412109</v>
       </c>
     </row>
     <row r="131">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>234.4518127441406</v>
+        <v>304.8545532226562</v>
       </c>
     </row>
     <row r="132">
@@ -2539,11 +2539,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>237.3331909179688</v>
+        <v>269.1281433105469</v>
       </c>
     </row>
     <row r="133">
@@ -2555,11 +2555,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>234.7080841064453</v>
+        <v>250.7725982666016</v>
       </c>
     </row>
     <row r="134">
@@ -2571,11 +2571,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>272.9317626953125</v>
+        <v>198.9098205566406</v>
       </c>
     </row>
     <row r="135">
@@ -2587,11 +2587,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>187.3390960693359</v>
+        <v>312.1837158203125</v>
       </c>
     </row>
     <row r="136">
@@ -2603,11 +2603,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>253.3988800048828</v>
+        <v>269.1924438476562</v>
       </c>
     </row>
     <row r="137">
@@ -2619,11 +2619,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>78.9259033203125</v>
+        <v>252.6756591796875</v>
       </c>
     </row>
     <row r="138">
@@ -2635,11 +2635,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>176.8258361816406</v>
+        <v>173.822998046875</v>
       </c>
     </row>
     <row r="139">
@@ -2651,11 +2651,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>102.0212326049805</v>
+        <v>136.4868316650391</v>
       </c>
     </row>
     <row r="140">
@@ -2667,11 +2667,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>98.40201568603516</v>
+        <v>335.5817260742188</v>
       </c>
     </row>
     <row r="141">
@@ -2683,11 +2683,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>67.63255310058594</v>
+        <v>223.5831604003906</v>
       </c>
     </row>
     <row r="142">
@@ -2699,11 +2699,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>15.0575704574585</v>
+        <v>823.8778076171875</v>
       </c>
     </row>
     <row r="143">
@@ -2715,11 +2715,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>39.48926544189453</v>
+        <v>758.8634033203125</v>
       </c>
     </row>
     <row r="144">
@@ -2731,11 +2731,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>33.25603485107422</v>
+        <v>530.01806640625</v>
       </c>
     </row>
     <row r="145">
@@ -2747,11 +2747,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>24.63466262817383</v>
+        <v>848.1298828125</v>
       </c>
     </row>
     <row r="146">
@@ -2763,11 +2763,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>90.56917572021484</v>
+        <v>436.6543579101562</v>
       </c>
     </row>
     <row r="147">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>62.71119689941406</v>
+        <v>812.0040283203125</v>
       </c>
     </row>
     <row r="148">
@@ -2795,11 +2795,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>42.4800910949707</v>
+        <v>284.583740234375</v>
       </c>
     </row>
     <row r="149">
@@ -2811,11 +2811,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>42.98527526855469</v>
+        <v>440.2485046386719</v>
       </c>
     </row>
     <row r="150">
@@ -2827,11 +2827,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>38.62979507446289</v>
+        <v>353.0538940429688</v>
       </c>
     </row>
     <row r="151">
@@ -2843,11 +2843,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>143.2204132080078</v>
+        <v>405.96923828125</v>
       </c>
     </row>
     <row r="152">
@@ -2859,11 +2859,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>252.3415374755859</v>
+        <v>509.2118835449219</v>
       </c>
     </row>
     <row r="153">
@@ -2875,11 +2875,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>256.3804626464844</v>
+        <v>470.6825866699219</v>
       </c>
     </row>
     <row r="154">
@@ -2891,11 +2891,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>176.8167114257812</v>
+        <v>369.6463623046875</v>
       </c>
     </row>
     <row r="155">
@@ -2907,11 +2907,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>233.7330474853516</v>
+        <v>551.3404541015625</v>
       </c>
     </row>
     <row r="156">
@@ -2923,11 +2923,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>182.0670776367188</v>
+        <v>547.457275390625</v>
       </c>
     </row>
     <row r="157">
@@ -2939,11 +2939,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>264.5072631835938</v>
+        <v>488.4326477050781</v>
       </c>
     </row>
     <row r="158">
@@ -2955,11 +2955,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>209.2861633300781</v>
+        <v>324.4856567382812</v>
       </c>
     </row>
     <row r="159">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>150.7274169921875</v>
+        <v>295.9659118652344</v>
       </c>
     </row>
     <row r="160">
@@ -2987,11 +2987,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>242.9825286865234</v>
+        <v>663.05908203125</v>
       </c>
     </row>
     <row r="161">
@@ -3003,11 +3003,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>97.54146575927734</v>
+        <v>364.2493896484375</v>
       </c>
     </row>
     <row r="162">
@@ -3019,11 +3019,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>253.0549163818359</v>
+        <v>784.0007934570312</v>
       </c>
     </row>
     <row r="163">
@@ -3035,11 +3035,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>245.6811370849609</v>
+        <v>748.541748046875</v>
       </c>
     </row>
     <row r="164">
@@ -3051,11 +3051,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>106.3414154052734</v>
+        <v>542.2550048828125</v>
       </c>
     </row>
     <row r="165">
@@ -3067,11 +3067,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>74.59880065917969</v>
+        <v>835.1854248046875</v>
       </c>
     </row>
     <row r="166">
@@ -3083,11 +3083,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>51.17644500732422</v>
+        <v>463.3468017578125</v>
       </c>
     </row>
     <row r="167">
@@ -3099,11 +3099,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>53.34446334838867</v>
+        <v>802.1151123046875</v>
       </c>
     </row>
     <row r="168">
@@ -3115,11 +3115,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>37.26594924926758</v>
+        <v>303.4431457519531</v>
       </c>
     </row>
     <row r="169">
@@ -3131,11 +3131,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>35.5529670715332</v>
+        <v>549.5673828125</v>
       </c>
     </row>
     <row r="170">
@@ -3147,11 +3147,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>128.2353363037109</v>
+        <v>391.0142517089844</v>
       </c>
     </row>
     <row r="171">
@@ -3163,11 +3163,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>88.53206634521484</v>
+        <v>429.6308898925781</v>
       </c>
     </row>
     <row r="172">
@@ -3179,11 +3179,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>72.82962036132812</v>
+        <v>580.9921875</v>
       </c>
     </row>
     <row r="173">
@@ -3195,11 +3195,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>69.97084045410156</v>
+        <v>536.7075805664062</v>
       </c>
     </row>
     <row r="174">
@@ -3211,11 +3211,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>54.01980590820312</v>
+        <v>436.3660583496094</v>
       </c>
     </row>
     <row r="175">
@@ -3227,11 +3227,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>160.0332946777344</v>
+        <v>617.4385986328125</v>
       </c>
     </row>
     <row r="176">
@@ -3243,11 +3243,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>271.1751098632812</v>
+        <v>696.474365234375</v>
       </c>
     </row>
     <row r="177">
@@ -3259,11 +3259,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>255.2664642333984</v>
+        <v>535.3419189453125</v>
       </c>
     </row>
     <row r="178">
@@ -3275,11 +3275,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>232.7653961181641</v>
+        <v>400.363037109375</v>
       </c>
     </row>
     <row r="179">
@@ -3291,11 +3291,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>282.4505920410156</v>
+        <v>372.4214172363281</v>
       </c>
     </row>
     <row r="180">
@@ -3307,11 +3307,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>247.9796447753906</v>
+        <v>840.0941162109375</v>
       </c>
     </row>
     <row r="181">
@@ -3323,11 +3323,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>283.9029541015625</v>
+        <v>450.4322509765625</v>
       </c>
     </row>
     <row r="182">
@@ -3339,11 +3339,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>294.4512023925781</v>
+        <v>658.6130981445312</v>
       </c>
     </row>
     <row r="183">
@@ -3355,11 +3355,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>211.3210906982422</v>
+        <v>590.4775390625</v>
       </c>
     </row>
     <row r="184">
@@ -3371,11 +3371,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>291.7019653320312</v>
+        <v>487.786376953125</v>
       </c>
     </row>
     <row r="185">
@@ -3387,11 +3387,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>125.6115646362305</v>
+        <v>756.2666625976562</v>
       </c>
     </row>
     <row r="186">
@@ -3403,11 +3403,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>234.4402313232422</v>
+        <v>504.3008117675781</v>
       </c>
     </row>
     <row r="187">
@@ -3419,11 +3419,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>119.3237915039062</v>
+        <v>663.775390625</v>
       </c>
     </row>
     <row r="188">
@@ -3435,11 +3435,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>136.6907348632812</v>
+        <v>347.8762512207031</v>
       </c>
     </row>
     <row r="189">
@@ -3451,11 +3451,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>102.9867095947266</v>
+        <v>590.84228515625</v>
       </c>
     </row>
     <row r="190">
@@ -3467,11 +3467,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>80.19303131103516</v>
+        <v>459.7835388183594</v>
       </c>
     </row>
     <row r="191">
@@ -3483,11 +3483,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>83.69395446777344</v>
+        <v>442.4892883300781</v>
       </c>
     </row>
     <row r="192">
@@ -3499,11 +3499,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>67.61547088623047</v>
+        <v>735.157958984375</v>
       </c>
     </row>
     <row r="193">
@@ -3515,11 +3515,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>67.33102416992188</v>
+        <v>628.527587890625</v>
       </c>
     </row>
     <row r="194">
@@ -3531,11 +3531,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>59.75513458251953</v>
+        <v>533.8381958007812</v>
       </c>
     </row>
     <row r="195">
@@ -3547,11 +3547,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>32.68937683105469</v>
+        <v>807.81982421875</v>
       </c>
     </row>
     <row r="196">
@@ -3563,11 +3563,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>12.43350696563721</v>
+        <v>917.0648193359375</v>
       </c>
     </row>
     <row r="197">
@@ -3579,11 +3579,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>11.15525817871094</v>
+        <v>648.6187133789062</v>
       </c>
     </row>
     <row r="198">
@@ -3595,11 +3595,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>10.82758140563965</v>
+        <v>558.6011352539062</v>
       </c>
     </row>
     <row r="199">
@@ -3611,11 +3611,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>101.1210250854492</v>
+        <v>478.7567749023438</v>
       </c>
     </row>
     <row r="200">
@@ -3627,11 +3627,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>182.5142517089844</v>
+        <v>1198.044921875</v>
       </c>
     </row>
     <row r="201">
@@ -3643,11 +3643,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>212.994873046875</v>
+        <v>595.5225830078125</v>
       </c>
     </row>
     <row r="202">
@@ -3659,11 +3659,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>168.0523071289062</v>
+        <v>747.5384521484375</v>
       </c>
     </row>
     <row r="203">
@@ -3675,11 +3675,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>237.6784362792969</v>
+        <v>698.391357421875</v>
       </c>
     </row>
     <row r="204">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>188.8164672851562</v>
+        <v>570.1119384765625</v>
       </c>
     </row>
     <row r="205">
@@ -3707,11 +3707,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>236.22607421875</v>
+        <v>847.0345458984375</v>
       </c>
     </row>
     <row r="206">
@@ -3723,11 +3723,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>190.6259613037109</v>
+        <v>605.21875</v>
       </c>
     </row>
     <row r="207">
@@ -3739,11 +3739,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>130.6444244384766</v>
+        <v>774.8433837890625</v>
       </c>
     </row>
     <row r="208">
@@ -3755,11 +3755,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>203.2953186035156</v>
+        <v>405.6235656738281</v>
       </c>
     </row>
     <row r="209">
@@ -3771,11 +3771,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>65.97593688964844</v>
+        <v>626.0648803710938</v>
       </c>
     </row>
     <row r="210">
@@ -3787,11 +3787,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>143.8938598632812</v>
+        <v>597.7451171875</v>
       </c>
     </row>
     <row r="211">
@@ -3803,11 +3803,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>221.1731567382812</v>
+        <v>520.3263549804688</v>
       </c>
     </row>
     <row r="212">
@@ -3819,11 +3819,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>83.46800231933594</v>
+        <v>842.50634765625</v>
       </c>
     </row>
     <row r="213">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>21.88727378845215</v>
+        <v>774.0768432617188</v>
       </c>
     </row>
     <row r="214">
@@ -3851,11 +3851,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>5.443427562713623</v>
+        <v>645.775146484375</v>
       </c>
     </row>
     <row r="215">
@@ -3867,11 +3867,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>16.77605819702148</v>
+        <v>938.0360717773438</v>
       </c>
     </row>
     <row r="216">
@@ -3883,11 +3883,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>9.069125175476074</v>
+        <v>1215.638549804688</v>
       </c>
     </row>
     <row r="217">
@@ -3899,11 +3899,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.6961072683334351</v>
+        <v>855.2076416015625</v>
       </c>
     </row>
     <row r="218">
@@ -3915,11 +3915,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>95.99855804443359</v>
+        <v>678.4542236328125</v>
       </c>
     </row>
     <row r="219">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>60.28057479858398</v>
+        <v>549.7858276367188</v>
       </c>
     </row>
     <row r="220">
@@ -3947,11 +3947,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>42.65361404418945</v>
+        <v>1739.09375</v>
       </c>
     </row>
     <row r="221">
@@ -3963,11 +3963,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>37.01620483398438</v>
+        <v>731.6829223632812</v>
       </c>
     </row>
     <row r="222">
@@ -3979,11 +3979,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>26.08825492858887</v>
+        <v>989.4161376953125</v>
       </c>
     </row>
     <row r="223">
@@ -3995,11 +3995,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>130.0246429443359</v>
+        <v>936.5640869140625</v>
       </c>
     </row>
     <row r="224">
@@ -4011,11 +4011,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>201.5351104736328</v>
+        <v>725.5843505859375</v>
       </c>
     </row>
     <row r="225">
@@ -4027,11 +4027,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>216.0898132324219</v>
+        <v>1091.698974609375</v>
       </c>
     </row>
     <row r="226">
@@ -4043,11 +4043,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>225.2266082763672</v>
+        <v>783.6688232421875</v>
       </c>
     </row>
     <row r="227">
@@ -4059,11 +4059,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>283.1046142578125</v>
+        <v>992.5474853515625</v>
       </c>
     </row>
     <row r="228">
@@ -4075,11 +4075,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>254.7403869628906</v>
+        <v>490.9303283691406</v>
       </c>
     </row>
     <row r="229">
@@ -4091,11 +4091,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>257.5324096679688</v>
+        <v>629.7977294921875</v>
       </c>
     </row>
     <row r="230">
@@ -4107,11 +4107,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>277.1789855957031</v>
+        <v>742.3070678710938</v>
       </c>
     </row>
     <row r="231">
@@ -4123,11 +4123,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>191.9575347900391</v>
+        <v>592.7401123046875</v>
       </c>
     </row>
     <row r="232">
@@ -4139,11 +4139,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>241.8567352294922</v>
+        <v>1032.709838867188</v>
       </c>
     </row>
     <row r="233">
@@ -4155,11 +4155,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>93.91670227050781</v>
+        <v>975.5929565429688</v>
       </c>
     </row>
     <row r="234">
@@ -4171,11 +4171,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>133.2965545654297</v>
+        <v>834.1314697265625</v>
       </c>
     </row>
     <row r="235">
@@ -4187,11 +4187,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>118.6913986206055</v>
+        <v>1125.134765625</v>
       </c>
     </row>
     <row r="236">
@@ -4203,11 +4203,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>113.6880874633789</v>
+        <v>1535.494506835938</v>
       </c>
     </row>
     <row r="237">
@@ -4219,11 +4219,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>52.10729598999023</v>
+        <v>995.975830078125</v>
       </c>
     </row>
     <row r="238">
@@ -4235,11 +4235,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>34.33056259155273</v>
+        <v>763.8158569335938</v>
       </c>
     </row>
     <row r="239">
@@ -4251,11 +4251,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>46.99609756469727</v>
+        <v>537.5671997070312</v>
       </c>
     </row>
     <row r="240">
@@ -4267,11 +4267,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>39.2891960144043</v>
+        <v>2044.526977539062</v>
       </c>
     </row>
     <row r="241">
@@ -4283,11 +4283,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>32.34474945068359</v>
+        <v>836.4243774414062</v>
       </c>
     </row>
     <row r="242">
@@ -4299,11 +4299,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>69.82172393798828</v>
+        <v>1093.8603515625</v>
       </c>
     </row>
     <row r="243">
@@ -4315,11 +4315,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>42.25304794311523</v>
+        <v>1039.541381835938</v>
       </c>
     </row>
     <row r="244">
@@ -4331,11 +4331,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>21.73268699645996</v>
+        <v>833.9200439453125</v>
       </c>
     </row>
     <row r="245">
@@ -4347,11 +4347,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>19.62366104125977</v>
+        <v>1169.395385742188</v>
       </c>
     </row>
     <row r="246">
@@ -4363,11 +4363,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>19.49741172790527</v>
+        <v>921.7838134765625</v>
       </c>
     </row>
     <row r="247">
@@ -4379,11 +4379,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>118.7625503540039</v>
+        <v>1103.788452148438</v>
       </c>
     </row>
     <row r="248">
@@ -4395,11 +4395,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>234.2254180908203</v>
+        <v>533.84765625</v>
       </c>
     </row>
     <row r="249">
@@ -4411,11 +4411,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>203.1591796875</v>
+        <v>544.0804443359375</v>
       </c>
     </row>
     <row r="250">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>174.2462921142578</v>
+        <v>861.8859252929688</v>
       </c>
     </row>
     <row r="251">
@@ -4443,11 +4443,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>216.5462799072266</v>
+        <v>658.1106567382812</v>
       </c>
     </row>
     <row r="252">
@@ -4459,11 +4459,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>164.4015655517578</v>
+        <v>1180.306274414062</v>
       </c>
     </row>
     <row r="253">
@@ -4475,11 +4475,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>247.9416656494141</v>
+        <v>1145.791137695312</v>
       </c>
     </row>
     <row r="254">
@@ -4491,11 +4491,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>184.0544281005859</v>
+        <v>984.169921875</v>
       </c>
     </row>
     <row r="255">
@@ -4507,11 +4507,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>144.1386413574219</v>
+        <v>1250.469116210938</v>
       </c>
     </row>
     <row r="256">
@@ -4523,11 +4523,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>210.6431884765625</v>
+        <v>1653.072875976562</v>
       </c>
     </row>
     <row r="257">
@@ -4539,11 +4539,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>80.23541259765625</v>
+        <v>1134.399658203125</v>
       </c>
     </row>
     <row r="258">
@@ -4555,11 +4555,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>227.5323944091797</v>
+        <v>821.2521362304688</v>
       </c>
     </row>
     <row r="259">
@@ -4571,11 +4571,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>188.2097625732422</v>
+        <v>481.2216491699219</v>
       </c>
     </row>
     <row r="260">
@@ -4587,11 +4587,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>82.51795959472656</v>
+        <v>2046.7705078125</v>
       </c>
     </row>
     <row r="261">
@@ -4603,11 +4603,11 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>44.19339752197266</v>
+        <v>884.2322387695312</v>
       </c>
     </row>
     <row r="262">
@@ -4619,11 +4619,11 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>39.71273422241211</v>
+        <v>992.2400512695312</v>
       </c>
     </row>
     <row r="263">
@@ -4635,11 +4635,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>26.92765045166016</v>
+        <v>939.8099975585938</v>
       </c>
     </row>
     <row r="264">
@@ -4651,11 +4651,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>15.1434440612793</v>
+        <v>749.71533203125</v>
       </c>
     </row>
     <row r="265">
@@ -4667,11 +4667,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>3.208868265151978</v>
+        <v>1069.910522460938</v>
       </c>
     </row>
     <row r="266">
@@ -4683,11 +4683,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>102.2370452880859</v>
+        <v>857.2947998046875</v>
       </c>
     </row>
     <row r="267">
@@ -4699,11 +4699,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>66.01619720458984</v>
+        <v>991.0255126953125</v>
       </c>
     </row>
     <row r="268">
@@ -4715,11 +4715,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>48.12469863891602</v>
+        <v>439.3576965332031</v>
       </c>
     </row>
     <row r="269">
@@ -4731,11 +4731,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>42.65169143676758</v>
+        <v>436.8722839355469</v>
       </c>
     </row>
     <row r="270">
@@ -4747,11 +4747,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>30.92998886108398</v>
+        <v>819.6477661132812</v>
       </c>
     </row>
     <row r="271">
@@ -4763,11 +4763,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>128.20361328125</v>
+        <v>566.5073852539062</v>
       </c>
     </row>
     <row r="272">
@@ -4779,11 +4779,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>250.2763519287109</v>
+        <v>1150.505249023438</v>
       </c>
     </row>
     <row r="273">
@@ -4795,11 +4795,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>207.5318298339844</v>
+        <v>1124.450805664062</v>
       </c>
     </row>
     <row r="274">
@@ -4811,11 +4811,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>227.5924682617188</v>
+        <v>947.1748657226562</v>
       </c>
     </row>
     <row r="275">
@@ -4827,11 +4827,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>256.12109375</v>
+        <v>1204.82666015625</v>
       </c>
     </row>
     <row r="276">
@@ -4843,11 +4843,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>226.3566131591797</v>
+        <v>1560.810424804688</v>
       </c>
     </row>
     <row r="277">
@@ -4859,11 +4859,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>263.3795471191406</v>
+        <v>1086.99267578125</v>
       </c>
     </row>
     <row r="278">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>266.1549682617188</v>
+        <v>678.79736328125</v>
       </c>
     </row>
     <row r="279">
@@ -4891,11 +4891,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>202.1679840087891</v>
+        <v>385.1805725097656</v>
       </c>
     </row>
     <row r="280">
@@ -4907,11 +4907,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>247.8726043701172</v>
+        <v>1844.10302734375</v>
       </c>
     </row>
     <row r="281">
@@ -4923,11 +4923,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>104.3480758666992</v>
+        <v>789.1905517578125</v>
       </c>
     </row>
     <row r="282">
@@ -4939,11 +4939,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>205.9118957519531</v>
+        <v>950.5046997070312</v>
       </c>
     </row>
     <row r="283">
@@ -4955,11 +4955,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>88.04341888427734</v>
+        <v>880.2997436523438</v>
       </c>
     </row>
     <row r="284">
@@ -4971,11 +4971,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>108.9099426269531</v>
+        <v>702.72216796875</v>
       </c>
     </row>
     <row r="285">
@@ -4987,11 +4987,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>68.62387847900391</v>
+        <v>1038.521728515625</v>
       </c>
     </row>
     <row r="286">
@@ -5003,11 +5003,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>64.77184295654297</v>
+        <v>873.3613891601562</v>
       </c>
     </row>
     <row r="287">
@@ -5019,11 +5019,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>53.31959533691406</v>
+        <v>943.3134155273438</v>
       </c>
     </row>
     <row r="288">
@@ -5035,11 +5035,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>41.53541946411133</v>
+        <v>408.5849609375</v>
       </c>
     </row>
     <row r="289">
@@ -5051,11 +5051,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>31.02944564819336</v>
+        <v>440.6246337890625</v>
       </c>
     </row>
     <row r="290">
@@ -5067,11 +5067,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>28.62493705749512</v>
+        <v>847.462890625</v>
       </c>
     </row>
     <row r="291">
@@ -5083,11 +5083,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>3.378762483596802</v>
+        <v>502.1429443359375</v>
       </c>
     </row>
     <row r="292">
@@ -5099,11 +5099,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>11.33221244812012</v>
+        <v>1167.376220703125</v>
       </c>
     </row>
     <row r="293">
@@ -5115,11 +5115,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>3.196584224700928</v>
+        <v>1125.514526367188</v>
       </c>
     </row>
     <row r="294">
@@ -5131,11 +5131,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>10.14678287506104</v>
+        <v>916.344970703125</v>
       </c>
     </row>
     <row r="295">
@@ -5147,11 +5147,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>69.04907989501953</v>
+        <v>1219.851806640625</v>
       </c>
     </row>
     <row r="296">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>151.3190765380859</v>
+        <v>1569.843994140625</v>
       </c>
     </row>
     <row r="297">
@@ -5179,11 +5179,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>190.8694610595703</v>
+        <v>1098.05322265625</v>
       </c>
     </row>
     <row r="298">
@@ -5195,11 +5195,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>138.3065490722656</v>
+        <v>639.3236083984375</v>
       </c>
     </row>
     <row r="299">
@@ -5211,11 +5211,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>216.0868682861328</v>
+        <v>396.7190856933594</v>
       </c>
     </row>
     <row r="300">
@@ -5227,11 +5227,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>149.9762115478516</v>
+        <v>1821.574096679688</v>
       </c>
     </row>
     <row r="301">
@@ -5243,11 +5243,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>127.7175903320312</v>
+        <v>705.9782104492188</v>
       </c>
     </row>
     <row r="302">
@@ -5259,11 +5259,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>120.0029602050781</v>
+        <v>947.68359375</v>
       </c>
     </row>
     <row r="303">
@@ -5275,11 +5275,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>48.30732727050781</v>
+        <v>873.4618530273438</v>
       </c>
     </row>
     <row r="304">
@@ -5291,11 +5291,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>66.76361846923828</v>
+        <v>694.1362915039062</v>
       </c>
     </row>
     <row r="305">
@@ -5307,11 +5307,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>36.61049652099609</v>
+        <v>1035.97998046875</v>
       </c>
     </row>
     <row r="306">
@@ -5323,11 +5323,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>79.16947174072266</v>
+        <v>870.708740234375</v>
       </c>
     </row>
     <row r="307">
@@ -5339,11 +5339,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>206.3406982421875</v>
+        <v>951.7545776367188</v>
       </c>
     </row>
     <row r="308">
@@ -5355,11 +5355,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>44.73667526245117</v>
+        <v>389.212890625</v>
       </c>
     </row>
     <row r="309">
@@ -5371,11 +5371,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0</v>
+        <v>441.21044921875</v>
       </c>
     </row>
     <row r="310">
@@ -5387,11 +5387,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>846.9552612304688</v>
       </c>
     </row>
     <row r="311">
@@ -5403,11 +5403,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0</v>
+        <v>493.2293090820312</v>
       </c>
     </row>
     <row r="312">
@@ -5419,11 +5419,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>0</v>
+        <v>1144.576171875</v>
       </c>
     </row>
     <row r="313">
@@ -5435,11 +5435,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0</v>
+        <v>1101.890869140625</v>
       </c>
     </row>
     <row r="314">
@@ -5451,11 +5451,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>49.92050933837891</v>
+        <v>892.2705078125</v>
       </c>
     </row>
     <row r="315">
@@ -5467,11 +5467,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>14.50371170043945</v>
+        <v>1185.617553710938</v>
       </c>
     </row>
     <row r="316">
@@ -5483,11 +5483,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>26.6044979095459</v>
+        <v>1504.303100585938</v>
       </c>
     </row>
     <row r="317">
@@ -5499,11 +5499,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>14.10975551605225</v>
+        <v>1076.551025390625</v>
       </c>
     </row>
     <row r="318">
@@ -5515,11 +5515,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>10.45959186553955</v>
+        <v>581.9931640625</v>
       </c>
     </row>
     <row r="319">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>83.00490570068359</v>
+        <v>383.1364440917969</v>
       </c>
     </row>
     <row r="320">
@@ -5547,11 +5547,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>155.3919982910156</v>
+        <v>1714.498901367188</v>
       </c>
     </row>
     <row r="321">
@@ -5563,11 +5563,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>188.4606475830078</v>
+        <v>663.8112182617188</v>
       </c>
     </row>
     <row r="322">
@@ -5579,11 +5579,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>180.5328979492188</v>
+        <v>1375.476196289062</v>
       </c>
     </row>
     <row r="323">
@@ -5595,11 +5595,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>245.369140625</v>
+        <v>1291.45654296875</v>
       </c>
     </row>
     <row r="324">
@@ -5611,11 +5611,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>200.9523010253906</v>
+        <v>1038.555908203125</v>
       </c>
     </row>
     <row r="325">
@@ -5627,11 +5627,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>134.0759582519531</v>
+        <v>1432.242919921875</v>
       </c>
     </row>
     <row r="326">
@@ -5643,11 +5643,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>190.010009765625</v>
+        <v>1028.018188476562</v>
       </c>
     </row>
     <row r="327">
@@ -5659,11 +5659,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>96.06558227539062</v>
+        <v>1308.913330078125</v>
       </c>
     </row>
     <row r="328">
@@ -5675,11 +5675,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>92.09075927734375</v>
+        <v>477.3320922851562</v>
       </c>
     </row>
     <row r="329">
@@ -5691,11 +5691,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>49.60345077514648</v>
+        <v>585.1220092773438</v>
       </c>
     </row>
     <row r="330">
@@ -5707,11 +5707,11 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>53.62430572509766</v>
+        <v>920.5345458984375</v>
       </c>
     </row>
     <row r="331">
@@ -5723,11 +5723,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>81.62644958496094</v>
+        <v>658.774169921875</v>
       </c>
     </row>
     <row r="332">
@@ -5739,11 +5739,11 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>60.00893783569336</v>
+        <v>1126.198974609375</v>
       </c>
     </row>
     <row r="333">
@@ -5755,11 +5755,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>11.16781711578369</v>
+        <v>1053.239624023438</v>
       </c>
     </row>
     <row r="334">
@@ -5771,11 +5771,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>0</v>
+        <v>853.0115356445312</v>
       </c>
     </row>
     <row r="335">
@@ -5787,11 +5787,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>14.52657127380371</v>
+        <v>1156.009643554688</v>
       </c>
     </row>
     <row r="336">
@@ -5803,11 +5803,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>4.039443492889404</v>
+        <v>1316.700317382812</v>
       </c>
     </row>
     <row r="337">
@@ -5819,11 +5819,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>4.425427436828613</v>
+        <v>1041.5732421875</v>
       </c>
     </row>
     <row r="338">
@@ -5835,11 +5835,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>30.50230598449707</v>
+        <v>468.3713989257812</v>
       </c>
     </row>
     <row r="339">
@@ -5851,11 +5851,11 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>5.256124973297119</v>
+        <v>356.9785766601562</v>
       </c>
     </row>
     <row r="340">
@@ -5867,11 +5867,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>13.20957088470459</v>
+        <v>1468.635864257812</v>
       </c>
     </row>
     <row r="341">
@@ -5883,11 +5883,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>5.07394552230835</v>
+        <v>557.0585327148438</v>
       </c>
     </row>
     <row r="342">
@@ -5899,11 +5899,11 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>12.02413940429688</v>
+        <v>1781.177001953125</v>
       </c>
     </row>
     <row r="343">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>70.05077362060547</v>
+        <v>1685.403076171875</v>
       </c>
     </row>
     <row r="344">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>157.8410491943359</v>
+        <v>1365.389770507812</v>
       </c>
     </row>
     <row r="345">
@@ -5947,11 +5947,11 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>195.5510711669922</v>
+        <v>1752.208862304688</v>
       </c>
     </row>
     <row r="346">
@@ -5963,11 +5963,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>145.3343658447266</v>
+        <v>1314.573974609375</v>
       </c>
     </row>
     <row r="347">
@@ -5979,11 +5979,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>210.6373748779297</v>
+        <v>1685.399047851562</v>
       </c>
     </row>
     <row r="348">
@@ -5995,11 +5995,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>149.3174438476562</v>
+        <v>603.0194702148438</v>
       </c>
     </row>
     <row r="349">
@@ -6011,11 +6011,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>129.2042541503906</v>
+        <v>795.7299194335938</v>
       </c>
     </row>
     <row r="350">
@@ -6027,11 +6027,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>119.5856323242188</v>
+        <v>1083.063232421875</v>
       </c>
     </row>
     <row r="351">
@@ -6043,11 +6043,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>50.18468856811523</v>
+        <v>798.6575927734375</v>
       </c>
     </row>
     <row r="352">
@@ -6059,11 +6059,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>67.82908630371094</v>
+        <v>972.8511962890625</v>
       </c>
     </row>
     <row r="353">
@@ -6075,11 +6075,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>38.48786163330078</v>
+        <v>894.3946533203125</v>
       </c>
     </row>
     <row r="354">
@@ -6091,11 +6091,11 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>84.21871948242188</v>
+        <v>719.7811889648438</v>
       </c>
     </row>
     <row r="355">
@@ -6107,11 +6107,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>216.0745391845703</v>
+        <v>1031.623046875</v>
       </c>
     </row>
     <row r="356">
@@ -6123,11 +6123,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>46.61403656005859</v>
+        <v>1108.304443359375</v>
       </c>
     </row>
     <row r="357">
@@ -6139,11 +6139,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0</v>
+        <v>904.7000732421875</v>
       </c>
     </row>
     <row r="358">
@@ -6155,11 +6155,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0</v>
+        <v>363.3750915527344</v>
       </c>
     </row>
     <row r="359">
@@ -6171,11 +6171,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>0</v>
+        <v>373.3920288085938</v>
       </c>
     </row>
     <row r="360">
@@ -6187,11 +6187,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>1185.423583984375</v>
       </c>
     </row>
     <row r="361">
@@ -6203,11 +6203,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>0</v>
+        <v>442.0063171386719</v>
       </c>
     </row>
     <row r="362">
@@ -6219,11 +6219,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>49.84359359741211</v>
+        <v>1754.410522460938</v>
       </c>
     </row>
     <row r="363">
@@ -6235,11 +6235,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>14.42679977416992</v>
+        <v>1662.613159179688</v>
       </c>
     </row>
     <row r="364">
@@ -6251,11 +6251,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>26.52758979797363</v>
+        <v>1343.019653320312</v>
       </c>
     </row>
     <row r="365">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>14.03284358978271</v>
+        <v>1725.586791992188</v>
       </c>
     </row>
     <row r="366">
@@ -6283,11 +6283,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>10.38268184661865</v>
+        <v>1333.607543945312</v>
       </c>
     </row>
     <row r="367">
@@ -6299,11 +6299,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>82.05233764648438</v>
+        <v>1661.825561523438</v>
       </c>
     </row>
     <row r="368">
@@ -6315,11 +6315,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>159.9596862792969</v>
+        <v>594.1670532226562</v>
       </c>
     </row>
     <row r="369">
@@ -6331,11 +6331,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>191.1879730224609</v>
+        <v>786.0247192382812</v>
       </c>
     </row>
     <row r="370">
@@ -6347,11 +6347,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>185.6064453125</v>
+        <v>1085.397583007812</v>
       </c>
     </row>
     <row r="371">
@@ -6363,11 +6363,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>237.9653625488281</v>
+        <v>788.932861328125</v>
       </c>
     </row>
     <row r="372">
@@ -6379,11 +6379,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>198.3392486572266</v>
+        <v>955.4251708984375</v>
       </c>
     </row>
     <row r="373">
@@ -6395,11 +6395,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>133.6083526611328</v>
+        <v>879.05712890625</v>
       </c>
     </row>
     <row r="374">
@@ -6411,11 +6411,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>187.6384124755859</v>
+        <v>705.9114990234375</v>
       </c>
     </row>
     <row r="375">
@@ -6427,11 +6427,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>97.40336608886719</v>
+        <v>1013.504760742188</v>
       </c>
     </row>
     <row r="376">
@@ -6443,11 +6443,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>91.20193481445312</v>
+        <v>1088.38134765625</v>
       </c>
     </row>
     <row r="377">
@@ -6459,11 +6459,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>49.52653503417969</v>
+        <v>889.898193359375</v>
       </c>
     </row>
     <row r="378">
@@ -6475,11 +6475,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>56.71927642822266</v>
+        <v>357.36865234375</v>
       </c>
     </row>
     <row r="379">
@@ -6491,11 +6491,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>89.406005859375</v>
+        <v>372.0809326171875</v>
       </c>
     </row>
     <row r="380">
@@ -6507,11 +6507,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>59.93202590942383</v>
+        <v>1158.680786132812</v>
       </c>
     </row>
     <row r="381">
@@ -6523,11 +6523,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>11.09090518951416</v>
+        <v>433.5469970703125</v>
       </c>
     </row>
     <row r="382">
@@ -6539,11 +6539,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>0</v>
+        <v>1542.679565429688</v>
       </c>
     </row>
     <row r="383">
@@ -6555,11 +6555,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>12.58750057220459</v>
+        <v>1496.888793945312</v>
       </c>
     </row>
     <row r="384">
@@ -6571,11 +6571,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>3.96253228187561</v>
+        <v>1161.810424804688</v>
       </c>
     </row>
     <row r="385">
@@ -6587,11 +6587,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>4.348516941070557</v>
+        <v>1568.112426757812</v>
       </c>
     </row>
     <row r="386">
@@ -6603,11 +6603,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>28.62493705749512</v>
+        <v>1244.389892578125</v>
       </c>
     </row>
     <row r="387">
@@ -6619,11 +6619,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>3.378762483596802</v>
+        <v>1538.9375</v>
       </c>
     </row>
     <row r="388">
@@ -6635,11 +6635,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>11.33221244812012</v>
+        <v>496.7057800292969</v>
       </c>
     </row>
     <row r="389">
@@ -6651,11 +6651,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>3.196584224700928</v>
+        <v>643.5221557617188</v>
       </c>
     </row>
     <row r="390">
@@ -6667,11 +6667,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>10.14678287506104</v>
+        <v>1034.239990234375</v>
       </c>
     </row>
     <row r="391">
@@ -6683,11 +6683,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>69.04907989501953</v>
+        <v>681.8795776367188</v>
       </c>
     </row>
     <row r="392">
@@ -6699,11 +6699,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>151.3190765380859</v>
+        <v>821.8134155273438</v>
       </c>
     </row>
     <row r="393">
@@ -6715,11 +6715,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>190.8694610595703</v>
+        <v>756.8377685546875</v>
       </c>
     </row>
     <row r="394">
@@ -6731,11 +6731,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>138.3065490722656</v>
+        <v>590.7139282226562</v>
       </c>
     </row>
     <row r="395">
@@ -6747,11 +6747,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>216.0868682861328</v>
+        <v>895.2322998046875</v>
       </c>
     </row>
     <row r="396">
@@ -6763,11 +6763,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>149.9762115478516</v>
+        <v>957.8713989257812</v>
       </c>
     </row>
     <row r="397">
@@ -6779,11 +6779,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>127.7175903320312</v>
+        <v>761.0030517578125</v>
       </c>
     </row>
     <row r="398">
@@ -6795,11 +6795,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>120.0029602050781</v>
+        <v>278.545166015625</v>
       </c>
     </row>
     <row r="399">
@@ -6811,11 +6811,11 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>48.30732727050781</v>
+        <v>290.9179077148438</v>
       </c>
     </row>
     <row r="400">
@@ -6827,11 +6827,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>66.76361846923828</v>
+        <v>994.7994384765625</v>
       </c>
     </row>
     <row r="401">
@@ -6843,11 +6843,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>36.61049652099609</v>
+        <v>333.7919921875</v>
       </c>
     </row>
     <row r="402">
@@ -6859,11 +6859,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>79.16947174072266</v>
+        <v>1198.004272460938</v>
       </c>
     </row>
     <row r="403">
@@ -6875,11 +6875,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>206.3406982421875</v>
+        <v>1160.31884765625</v>
       </c>
     </row>
     <row r="404">
@@ -6891,11 +6891,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>44.73667526245117</v>
+        <v>929.0571899414062</v>
       </c>
     </row>
     <row r="405">
@@ -6907,11 +6907,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>0</v>
+        <v>1211.989135742188</v>
       </c>
     </row>
     <row r="406">
@@ -6923,11 +6923,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>0</v>
+        <v>996.7095947265625</v>
       </c>
     </row>
     <row r="407">
@@ -6939,11 +6939,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>0</v>
+        <v>1196.764282226562</v>
       </c>
     </row>
     <row r="408">
@@ -6955,11 +6955,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>0</v>
+        <v>380.9028015136719</v>
       </c>
     </row>
     <row r="409">
@@ -6971,11 +6971,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0</v>
+        <v>498.6449279785156</v>
       </c>
     </row>
     <row r="410">
@@ -6987,11 +6987,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>49.92050933837891</v>
+        <v>770.1676635742188</v>
       </c>
     </row>
     <row r="411">
@@ -7003,11 +7003,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>14.50371170043945</v>
+        <v>549.6390380859375</v>
       </c>
     </row>
     <row r="412">
@@ -7019,11 +7019,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>26.6044979095459</v>
+        <v>629.2685546875</v>
       </c>
     </row>
     <row r="413">
@@ -7035,11 +7035,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>14.10975551605225</v>
+        <v>599.782470703125</v>
       </c>
     </row>
     <row r="414">
@@ -7051,11 +7051,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>10.45959186553955</v>
+        <v>483.29833984375</v>
       </c>
     </row>
     <row r="415">
@@ -7067,11 +7067,11 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>83.00490570068359</v>
+        <v>677.6104125976562</v>
       </c>
     </row>
     <row r="416">
@@ -7083,11 +7083,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>155.3919982910156</v>
+        <v>710.7421264648438</v>
       </c>
     </row>
     <row r="417">
@@ -7099,11 +7099,11 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>188.4606475830078</v>
+        <v>575.0255737304688</v>
       </c>
     </row>
     <row r="418">
@@ -7115,11 +7115,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>180.5328979492188</v>
+        <v>188.8606109619141</v>
       </c>
     </row>
     <row r="419">
@@ -7131,11 +7131,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>245.369140625</v>
+        <v>189.2919464111328</v>
       </c>
     </row>
     <row r="420">
@@ -7147,11 +7147,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>200.9523010253906</v>
+        <v>693.370361328125</v>
       </c>
     </row>
     <row r="421">
@@ -7163,11 +7163,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>134.0759582519531</v>
+        <v>238.1995849609375</v>
       </c>
     </row>
     <row r="422">
@@ -7179,11 +7179,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>190.010009765625</v>
+        <v>695.0036010742188</v>
       </c>
     </row>
     <row r="423">
@@ -7195,11 +7195,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>96.06558227539062</v>
+        <v>634.9209594726562</v>
       </c>
     </row>
     <row r="424">
@@ -7211,11 +7211,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>92.09075927734375</v>
+        <v>504.069091796875</v>
       </c>
     </row>
     <row r="425">
@@ -7227,11 +7227,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>49.60345077514648</v>
+        <v>769.4197387695312</v>
       </c>
     </row>
     <row r="426">
@@ -7243,11 +7243,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>53.62430572509766</v>
+        <v>618.7008666992188</v>
       </c>
     </row>
     <row r="427">
@@ -7259,11 +7259,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>81.62644958496094</v>
+        <v>697.2710571289062</v>
       </c>
     </row>
     <row r="428">
@@ -7275,11 +7275,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>60.00893783569336</v>
+        <v>252.6450500488281</v>
       </c>
     </row>
     <row r="429">
@@ -7291,11 +7291,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>11.16781711578369</v>
+        <v>309.9620056152344</v>
       </c>
     </row>
     <row r="430">
@@ -7307,11 +7307,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>0</v>
+        <v>474.2478637695312</v>
       </c>
     </row>
     <row r="431">
@@ -7323,11 +7323,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>14.52657127380371</v>
+        <v>360.4958801269531</v>
       </c>
     </row>
     <row r="432">
@@ -7339,11 +7339,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>4.039443492889404</v>
+        <v>500.5557556152344</v>
       </c>
     </row>
     <row r="433">
@@ -7355,11 +7355,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>4.425427436828613</v>
+        <v>400.9274597167969</v>
       </c>
     </row>
     <row r="434">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>25.80452156066895</v>
+        <v>309.9468994140625</v>
       </c>
     </row>
     <row r="435">
@@ -7387,11 +7387,11 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>0.5583485960960388</v>
+        <v>554.9016723632812</v>
       </c>
     </row>
     <row r="436">
@@ -7403,11 +7403,11 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>8.511796951293945</v>
+        <v>504.0967712402344</v>
       </c>
     </row>
     <row r="437">
@@ -7419,11 +7419,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>0</v>
+        <v>389.4928283691406</v>
       </c>
     </row>
     <row r="438">
@@ -7435,11 +7435,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>7.326359272003174</v>
+        <v>100.7698669433594</v>
       </c>
     </row>
     <row r="439">
@@ -7451,11 +7451,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>63.20829010009766</v>
+        <v>94.91333770751953</v>
       </c>
     </row>
     <row r="440">
@@ -7467,11 +7467,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>151.3801574707031</v>
+        <v>480.1747131347656</v>
       </c>
     </row>
     <row r="441">
@@ -7483,11 +7483,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>184.0618133544922</v>
+        <v>170.5445709228516</v>
       </c>
     </row>
     <row r="442">
@@ -7499,11 +7499,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>135.4861297607422</v>
+        <v>492.6072998046875</v>
       </c>
     </row>
     <row r="443">
@@ -7515,11 +7515,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>200.8737640380859</v>
+        <v>449.4508972167969</v>
       </c>
     </row>
     <row r="444">
@@ -7531,11 +7531,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>146.6589508056641</v>
+        <v>348.6269836425781</v>
       </c>
     </row>
     <row r="445">
@@ -7547,11 +7547,11 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>127.564338684082</v>
+        <v>536.2726440429688</v>
       </c>
     </row>
     <row r="446">
@@ -7563,11 +7563,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>116.2087860107422</v>
+        <v>424.85791015625</v>
       </c>
     </row>
     <row r="447">
@@ -7579,11 +7579,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>52.02325439453125</v>
+        <v>493.4310913085938</v>
       </c>
     </row>
     <row r="448">
@@ -7595,11 +7595,11 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>65.65677642822266</v>
+        <v>196.0881042480469</v>
       </c>
     </row>
     <row r="449">
@@ -7611,11 +7611,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>31.79120635986328</v>
+        <v>211.1667938232422</v>
       </c>
     </row>
     <row r="450">
@@ -7627,11 +7627,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>76.34906768798828</v>
+        <v>324.6102905273438</v>
       </c>
     </row>
     <row r="451">
@@ -7643,11 +7643,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>199.0410461425781</v>
+        <v>268.1810302734375</v>
       </c>
     </row>
     <row r="452">
@@ -7659,11 +7659,11 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>41.91626358032227</v>
+        <v>376.4169616699219</v>
       </c>
     </row>
     <row r="453">
@@ -7675,11 +7675,11 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>0</v>
+        <v>314.42578125</v>
       </c>
     </row>
     <row r="454">
@@ -7691,11 +7691,11 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>0</v>
+        <v>219.9979248046875</v>
       </c>
     </row>
     <row r="455">
@@ -7707,11 +7707,11 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>0</v>
+        <v>400.4124145507812</v>
       </c>
     </row>
     <row r="456">
@@ -7723,11 +7723,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>0</v>
+        <v>372.2031555175781</v>
       </c>
     </row>
     <row r="457">
@@ -7739,11 +7739,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>工作日</t>
+          <t>周末</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>0</v>
+        <v>311.0075073242188</v>
       </c>
     </row>
     <row r="458">
@@ -7755,11 +7755,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>47.10008239746094</v>
+        <v>60.69991302490234</v>
       </c>
     </row>
     <row r="459">
@@ -7771,11 +7771,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>11.6832971572876</v>
+        <v>46.29832458496094</v>
       </c>
     </row>
     <row r="460">
@@ -7787,11 +7787,11 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>23.78407859802246</v>
+        <v>417.1415405273438</v>
       </c>
     </row>
     <row r="461">
@@ -7803,11 +7803,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>9.540475845336914</v>
+        <v>133.4061279296875</v>
       </c>
     </row>
     <row r="462">
@@ -7819,11 +7819,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>7.63917875289917</v>
+        <v>252.4496765136719</v>
       </c>
     </row>
     <row r="463">
@@ -7835,11 +7835,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>73.05048370361328</v>
+        <v>200.2494964599609</v>
       </c>
     </row>
     <row r="464">
@@ -7851,11 +7851,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>155.4530792236328</v>
+        <v>145.5133819580078</v>
       </c>
     </row>
     <row r="465">
@@ -7867,11 +7867,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>181.6529998779297</v>
+        <v>315.3228759765625</v>
       </c>
     </row>
     <row r="466">
@@ -7883,11 +7883,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>177.7124633789062</v>
+        <v>161.5384674072266</v>
       </c>
     </row>
     <row r="467">
@@ -7899,11 +7899,11 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>230.1560668945312</v>
+        <v>234.878173828125</v>
       </c>
     </row>
     <row r="468">
@@ -7915,11 +7915,11 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>197.6351165771484</v>
+        <v>46.56964111328125</v>
       </c>
     </row>
     <row r="469">
@@ -7931,11 +7931,11 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>133.9227142333984</v>
+        <v>49.188720703125</v>
       </c>
     </row>
     <row r="470">
@@ -7947,11 +7947,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>187.1896057128906</v>
+        <v>129.0003356933594</v>
       </c>
     </row>
     <row r="471">
@@ -7963,11 +7963,11 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>99.781494140625</v>
+        <v>121.8679885864258</v>
       </c>
     </row>
     <row r="472">
@@ -7979,11 +7979,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>89.27032470703125</v>
+        <v>250.9499816894531</v>
       </c>
     </row>
     <row r="473">
@@ -7995,11 +7995,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>44.78416061401367</v>
+        <v>182.8450317382812</v>
       </c>
     </row>
     <row r="474">
@@ -8011,11 +8011,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>50.80387878417969</v>
+        <v>127.5331573486328</v>
       </c>
     </row>
     <row r="475">
@@ -8027,11 +8027,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>71.09329223632812</v>
+        <v>265.0670471191406</v>
       </c>
     </row>
     <row r="476">
@@ -8043,11 +8043,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>57.18851852416992</v>
+        <v>173.0266265869141</v>
       </c>
     </row>
     <row r="477">
@@ -8059,11 +8059,11 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>8.347383499145508</v>
+        <v>168.1820373535156</v>
       </c>
     </row>
     <row r="478">
@@ -8075,11 +8075,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>0</v>
+        <v>1.781848430633545</v>
       </c>
     </row>
     <row r="479">
@@ -8091,11 +8091,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>6.24294900894165</v>
+        <v>0.8373221158981323</v>
       </c>
     </row>
     <row r="480">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>0</v>
+        <v>181.3551177978516</v>
       </c>
     </row>
     <row r="481">
@@ -8123,11 +8123,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>周末</t>
+          <t>工作日</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>0</v>
+        <v>56.57915878295898</v>
       </c>
     </row>
   </sheetData>
